--- a/Data/EC/NIT-9006450454.xlsx
+++ b/Data/EC/NIT-9006450454.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Documents\NIYARAKY\MACROS AJUSTADAS\2- MACRO COMFENALCO CARTAGENA ACTUALIZACION\Estados De Cuenta\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ysarm\OneDrive\Desktop\MACROS\2- MACRO COMFENALCO CARTAGENA ACTUALIZACION\Estados De Cuenta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{03E58BEB-728F-4294-A025-D9AB864B507A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{868382B9-9BE7-4A8B-A0C3-8D3C497E8AEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{2AA828E8-38B6-4B6E-894A-3AD86289EE63}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{08AA2BD9-A793-44B1-AEDC-4BFC813B56D4}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -71,6 +71,309 @@
     <t>RONAL BELLO RODRIGUEZ</t>
   </si>
   <si>
+    <t>2502</t>
+  </si>
+  <si>
+    <t>2501</t>
+  </si>
+  <si>
+    <t>2412</t>
+  </si>
+  <si>
+    <t>2411</t>
+  </si>
+  <si>
+    <t>2410</t>
+  </si>
+  <si>
+    <t>2409</t>
+  </si>
+  <si>
+    <t>2408</t>
+  </si>
+  <si>
+    <t>2407</t>
+  </si>
+  <si>
+    <t>2406</t>
+  </si>
+  <si>
+    <t>2405</t>
+  </si>
+  <si>
+    <t>2404</t>
+  </si>
+  <si>
+    <t>2403</t>
+  </si>
+  <si>
+    <t>2402</t>
+  </si>
+  <si>
+    <t>2401</t>
+  </si>
+  <si>
+    <t>2312</t>
+  </si>
+  <si>
+    <t>2311</t>
+  </si>
+  <si>
+    <t>2310</t>
+  </si>
+  <si>
+    <t>2309</t>
+  </si>
+  <si>
+    <t>2308</t>
+  </si>
+  <si>
+    <t>2307</t>
+  </si>
+  <si>
+    <t>2306</t>
+  </si>
+  <si>
+    <t>2305</t>
+  </si>
+  <si>
+    <t>2304</t>
+  </si>
+  <si>
+    <t>2303</t>
+  </si>
+  <si>
+    <t>2302</t>
+  </si>
+  <si>
+    <t>2301</t>
+  </si>
+  <si>
+    <t>2212</t>
+  </si>
+  <si>
+    <t>2211</t>
+  </si>
+  <si>
+    <t>2210</t>
+  </si>
+  <si>
+    <t>2209</t>
+  </si>
+  <si>
+    <t>2208</t>
+  </si>
+  <si>
+    <t>2207</t>
+  </si>
+  <si>
+    <t>2206</t>
+  </si>
+  <si>
+    <t>2205</t>
+  </si>
+  <si>
+    <t>2204</t>
+  </si>
+  <si>
+    <t>2203</t>
+  </si>
+  <si>
+    <t>2202</t>
+  </si>
+  <si>
+    <t>2201</t>
+  </si>
+  <si>
+    <t>2112</t>
+  </si>
+  <si>
+    <t>2111</t>
+  </si>
+  <si>
+    <t>2110</t>
+  </si>
+  <si>
+    <t>2109</t>
+  </si>
+  <si>
+    <t>2108</t>
+  </si>
+  <si>
+    <t>2107</t>
+  </si>
+  <si>
+    <t>2106</t>
+  </si>
+  <si>
+    <t>2105</t>
+  </si>
+  <si>
+    <t>2104</t>
+  </si>
+  <si>
+    <t>2103</t>
+  </si>
+  <si>
+    <t>2102</t>
+  </si>
+  <si>
+    <t>2101</t>
+  </si>
+  <si>
+    <t>2012</t>
+  </si>
+  <si>
+    <t>2011</t>
+  </si>
+  <si>
+    <t>2010</t>
+  </si>
+  <si>
+    <t>2009</t>
+  </si>
+  <si>
+    <t>2008</t>
+  </si>
+  <si>
+    <t>2007</t>
+  </si>
+  <si>
+    <t>2006</t>
+  </si>
+  <si>
+    <t>2005</t>
+  </si>
+  <si>
+    <t>2004</t>
+  </si>
+  <si>
+    <t>2003</t>
+  </si>
+  <si>
+    <t>2002</t>
+  </si>
+  <si>
+    <t>2001</t>
+  </si>
+  <si>
+    <t>1912</t>
+  </si>
+  <si>
+    <t>1911</t>
+  </si>
+  <si>
+    <t>1910</t>
+  </si>
+  <si>
+    <t>1909</t>
+  </si>
+  <si>
+    <t>1908</t>
+  </si>
+  <si>
+    <t>1907</t>
+  </si>
+  <si>
+    <t>1906</t>
+  </si>
+  <si>
+    <t>1905</t>
+  </si>
+  <si>
+    <t>1904</t>
+  </si>
+  <si>
+    <t>1903</t>
+  </si>
+  <si>
+    <t>1902</t>
+  </si>
+  <si>
+    <t>1901</t>
+  </si>
+  <si>
+    <t>1812</t>
+  </si>
+  <si>
+    <t>1811</t>
+  </si>
+  <si>
+    <t>1810</t>
+  </si>
+  <si>
+    <t>1809</t>
+  </si>
+  <si>
+    <t>1808</t>
+  </si>
+  <si>
+    <t>1807</t>
+  </si>
+  <si>
+    <t>1806</t>
+  </si>
+  <si>
+    <t>1805</t>
+  </si>
+  <si>
+    <t>1804</t>
+  </si>
+  <si>
+    <t>1803</t>
+  </si>
+  <si>
+    <t>1802</t>
+  </si>
+  <si>
+    <t>1801</t>
+  </si>
+  <si>
+    <t>1712</t>
+  </si>
+  <si>
+    <t>1711</t>
+  </si>
+  <si>
+    <t>1710</t>
+  </si>
+  <si>
+    <t>1709</t>
+  </si>
+  <si>
+    <t>1708</t>
+  </si>
+  <si>
+    <t>1707</t>
+  </si>
+  <si>
+    <t>1706</t>
+  </si>
+  <si>
+    <t>1705</t>
+  </si>
+  <si>
+    <t>1704</t>
+  </si>
+  <si>
+    <t>1703</t>
+  </si>
+  <si>
+    <t>1702</t>
+  </si>
+  <si>
+    <t>1701</t>
+  </si>
+  <si>
+    <t>1612</t>
+  </si>
+  <si>
+    <t>1611</t>
+  </si>
+  <si>
+    <t>1610</t>
+  </si>
+  <si>
     <t>1609</t>
   </si>
   <si>
@@ -78,309 +381,6 @@
   </si>
   <si>
     <t>KEVIN JESUS MARTINEZ DIMAS</t>
-  </si>
-  <si>
-    <t>1610</t>
-  </si>
-  <si>
-    <t>1611</t>
-  </si>
-  <si>
-    <t>1612</t>
-  </si>
-  <si>
-    <t>1701</t>
-  </si>
-  <si>
-    <t>1702</t>
-  </si>
-  <si>
-    <t>1703</t>
-  </si>
-  <si>
-    <t>1704</t>
-  </si>
-  <si>
-    <t>1705</t>
-  </si>
-  <si>
-    <t>1706</t>
-  </si>
-  <si>
-    <t>1707</t>
-  </si>
-  <si>
-    <t>1708</t>
-  </si>
-  <si>
-    <t>1709</t>
-  </si>
-  <si>
-    <t>1710</t>
-  </si>
-  <si>
-    <t>1711</t>
-  </si>
-  <si>
-    <t>1712</t>
-  </si>
-  <si>
-    <t>1801</t>
-  </si>
-  <si>
-    <t>1802</t>
-  </si>
-  <si>
-    <t>1803</t>
-  </si>
-  <si>
-    <t>1804</t>
-  </si>
-  <si>
-    <t>1805</t>
-  </si>
-  <si>
-    <t>1806</t>
-  </si>
-  <si>
-    <t>1807</t>
-  </si>
-  <si>
-    <t>1808</t>
-  </si>
-  <si>
-    <t>1809</t>
-  </si>
-  <si>
-    <t>1810</t>
-  </si>
-  <si>
-    <t>1811</t>
-  </si>
-  <si>
-    <t>1812</t>
-  </si>
-  <si>
-    <t>1901</t>
-  </si>
-  <si>
-    <t>1902</t>
-  </si>
-  <si>
-    <t>1903</t>
-  </si>
-  <si>
-    <t>1904</t>
-  </si>
-  <si>
-    <t>1905</t>
-  </si>
-  <si>
-    <t>1906</t>
-  </si>
-  <si>
-    <t>1907</t>
-  </si>
-  <si>
-    <t>1908</t>
-  </si>
-  <si>
-    <t>1909</t>
-  </si>
-  <si>
-    <t>1910</t>
-  </si>
-  <si>
-    <t>1911</t>
-  </si>
-  <si>
-    <t>1912</t>
-  </si>
-  <si>
-    <t>2001</t>
-  </si>
-  <si>
-    <t>2002</t>
-  </si>
-  <si>
-    <t>2003</t>
-  </si>
-  <si>
-    <t>2004</t>
-  </si>
-  <si>
-    <t>2005</t>
-  </si>
-  <si>
-    <t>2006</t>
-  </si>
-  <si>
-    <t>2007</t>
-  </si>
-  <si>
-    <t>2008</t>
-  </si>
-  <si>
-    <t>2009</t>
-  </si>
-  <si>
-    <t>2010</t>
-  </si>
-  <si>
-    <t>2011</t>
-  </si>
-  <si>
-    <t>2012</t>
-  </si>
-  <si>
-    <t>2101</t>
-  </si>
-  <si>
-    <t>2102</t>
-  </si>
-  <si>
-    <t>2103</t>
-  </si>
-  <si>
-    <t>2104</t>
-  </si>
-  <si>
-    <t>2105</t>
-  </si>
-  <si>
-    <t>2106</t>
-  </si>
-  <si>
-    <t>2107</t>
-  </si>
-  <si>
-    <t>2108</t>
-  </si>
-  <si>
-    <t>2109</t>
-  </si>
-  <si>
-    <t>2110</t>
-  </si>
-  <si>
-    <t>2111</t>
-  </si>
-  <si>
-    <t>2112</t>
-  </si>
-  <si>
-    <t>2201</t>
-  </si>
-  <si>
-    <t>2202</t>
-  </si>
-  <si>
-    <t>2203</t>
-  </si>
-  <si>
-    <t>2204</t>
-  </si>
-  <si>
-    <t>2205</t>
-  </si>
-  <si>
-    <t>2206</t>
-  </si>
-  <si>
-    <t>2207</t>
-  </si>
-  <si>
-    <t>2208</t>
-  </si>
-  <si>
-    <t>2209</t>
-  </si>
-  <si>
-    <t>2210</t>
-  </si>
-  <si>
-    <t>2211</t>
-  </si>
-  <si>
-    <t>2212</t>
-  </si>
-  <si>
-    <t>2301</t>
-  </si>
-  <si>
-    <t>2302</t>
-  </si>
-  <si>
-    <t>2303</t>
-  </si>
-  <si>
-    <t>2304</t>
-  </si>
-  <si>
-    <t>2305</t>
-  </si>
-  <si>
-    <t>2306</t>
-  </si>
-  <si>
-    <t>2307</t>
-  </si>
-  <si>
-    <t>2308</t>
-  </si>
-  <si>
-    <t>2309</t>
-  </si>
-  <si>
-    <t>2310</t>
-  </si>
-  <si>
-    <t>2311</t>
-  </si>
-  <si>
-    <t>2312</t>
-  </si>
-  <si>
-    <t>2401</t>
-  </si>
-  <si>
-    <t>2402</t>
-  </si>
-  <si>
-    <t>2403</t>
-  </si>
-  <si>
-    <t>2404</t>
-  </si>
-  <si>
-    <t>2405</t>
-  </si>
-  <si>
-    <t>2406</t>
-  </si>
-  <si>
-    <t>2407</t>
-  </si>
-  <si>
-    <t>2408</t>
-  </si>
-  <si>
-    <t>2409</t>
-  </si>
-  <si>
-    <t>2410</t>
-  </si>
-  <si>
-    <t>2411</t>
-  </si>
-  <si>
-    <t>2412</t>
-  </si>
-  <si>
-    <t>2501</t>
-  </si>
-  <si>
-    <t>2502</t>
   </si>
   <si>
     <t>ESTADO DE CUENTA</t>
@@ -479,9 +479,7 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
+      <right/>
       <top style="thin">
         <color indexed="64"/>
       </top>
@@ -494,7 +492,9 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
       <top style="thin">
         <color indexed="64"/>
       </top>
@@ -694,23 +694,23 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -738,10 +738,10 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -779,22 +779,22 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>667900</xdr:colOff>
+      <xdr:colOff>717113</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>62300</xdr:rowOff>
+      <xdr:rowOff>75000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>430650</xdr:colOff>
+      <xdr:colOff>435413</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>121850</xdr:rowOff>
+      <xdr:rowOff>115500</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="3" name="Imagen 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0351DE66-EB2E-FAE8-C2EE-1CAF8BE078BA}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CC96916C-8E77-C705-B29C-573E3C52C5F6}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -816,7 +816,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="921900" y="246450"/>
+          <a:off x="964763" y="265500"/>
           <a:ext cx="975600" cy="612000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1145,23 +1145,23 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C24D0650-34EB-4526-90E1-47B642F341D5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D66CA22-9AD6-486C-9A51-155998A61875}">
   <dimension ref="B2:J224"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.6328125" customWidth="1"/>
-    <col min="2" max="2" width="18.54296875" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.7265625" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="28.453125" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.54296875" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.1796875" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.36328125" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.36328125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.08984375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.7109375" customWidth="1"/>
+    <col min="2" max="2" width="19.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B2" s="3"/>
       <c r="C2" s="28"/>
       <c r="D2" s="29" t="s">
@@ -1174,7 +1174,7 @@
       <c r="I2" s="29"/>
       <c r="J2" s="29"/>
     </row>
-    <row r="3" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B3" s="3"/>
       <c r="C3" s="28"/>
       <c r="D3" s="30"/>
@@ -1185,7 +1185,7 @@
       <c r="I3" s="30"/>
       <c r="J3" s="30"/>
     </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B4" s="3"/>
       <c r="C4" s="28"/>
       <c r="D4" s="30"/>
@@ -1196,7 +1196,7 @@
       <c r="I4" s="30"/>
       <c r="J4" s="30"/>
     </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B5" s="3"/>
       <c r="C5" s="28"/>
       <c r="D5" s="31"/>
@@ -1207,8 +1207,8 @@
       <c r="I5" s="31"/>
       <c r="J5" s="31"/>
     </row>
-    <row r="6" spans="2:10" ht="9" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:10" ht="9" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B7" s="4" t="s">
         <v>116</v>
       </c>
@@ -1223,8 +1223,8 @@
       <c r="I7" s="6"/>
       <c r="J7" s="6"/>
     </row>
-    <row r="8" spans="2:10" ht="7.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:10" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B9" s="4" t="s">
         <v>6</v>
       </c>
@@ -1239,8 +1239,8 @@
       <c r="I9" s="6"/>
       <c r="J9" s="6"/>
     </row>
-    <row r="10" spans="2:10" ht="6.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:10" ht="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B11" s="4" t="s">
         <v>117</v>
       </c>
@@ -1255,8 +1255,8 @@
       <c r="I11" s="7"/>
       <c r="J11" s="7"/>
     </row>
-    <row r="12" spans="2:10" ht="4.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:10" ht="4.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B13" s="9" t="s">
         <v>118</v>
       </c>
@@ -1275,7 +1275,7 @@
       <c r="I13" s="5"/>
       <c r="J13" s="5"/>
     </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B15" s="10" t="s">
         <v>0</v>
       </c>
@@ -1304,7 +1304,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="16" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B16" s="15" t="s">
         <v>8</v>
       </c>
@@ -1318,7 +1318,7 @@
         <v>11</v>
       </c>
       <c r="F16" s="18">
-        <v>27578</v>
+        <v>19791</v>
       </c>
       <c r="G16" s="18">
         <v>781242</v>
@@ -1327,21 +1327,21 @@
       <c r="I16" s="19"/>
       <c r="J16" s="20"/>
     </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B17" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C17" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="D17" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="E17" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="E17" s="16" t="s">
-        <v>11</v>
-      </c>
       <c r="F17" s="18">
-        <v>27578</v>
+        <v>31249</v>
       </c>
       <c r="G17" s="18">
         <v>781242</v>
@@ -1350,7 +1350,7 @@
       <c r="I17" s="19"/>
       <c r="J17" s="20"/>
     </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B18" s="15" t="s">
         <v>8</v>
       </c>
@@ -1361,10 +1361,10 @@
         <v>10</v>
       </c>
       <c r="E18" s="16" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F18" s="18">
-        <v>27578</v>
+        <v>31249</v>
       </c>
       <c r="G18" s="18">
         <v>781242</v>
@@ -1373,21 +1373,21 @@
       <c r="I18" s="19"/>
       <c r="J18" s="20"/>
     </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B19" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C19" s="16" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D19" s="17" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E19" s="16" t="s">
         <v>14</v>
       </c>
       <c r="F19" s="18">
-        <v>27578</v>
+        <v>31249</v>
       </c>
       <c r="G19" s="18">
         <v>781242</v>
@@ -1396,7 +1396,7 @@
       <c r="I19" s="19"/>
       <c r="J19" s="20"/>
     </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B20" s="15" t="s">
         <v>8</v>
       </c>
@@ -1410,7 +1410,7 @@
         <v>15</v>
       </c>
       <c r="F20" s="18">
-        <v>27578</v>
+        <v>31249</v>
       </c>
       <c r="G20" s="18">
         <v>781242</v>
@@ -1419,21 +1419,21 @@
       <c r="I20" s="19"/>
       <c r="J20" s="20"/>
     </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B21" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C21" s="16" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D21" s="17" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E21" s="16" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F21" s="18">
-        <v>27578</v>
+        <v>31249</v>
       </c>
       <c r="G21" s="18">
         <v>781242</v>
@@ -1442,7 +1442,7 @@
       <c r="I21" s="19"/>
       <c r="J21" s="20"/>
     </row>
-    <row r="22" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B22" s="15" t="s">
         <v>8</v>
       </c>
@@ -1453,10 +1453,10 @@
         <v>10</v>
       </c>
       <c r="E22" s="16" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F22" s="18">
-        <v>27578</v>
+        <v>31249</v>
       </c>
       <c r="G22" s="18">
         <v>781242</v>
@@ -1465,21 +1465,21 @@
       <c r="I22" s="19"/>
       <c r="J22" s="20"/>
     </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B23" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C23" s="16" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D23" s="17" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E23" s="16" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F23" s="18">
-        <v>27578</v>
+        <v>31249</v>
       </c>
       <c r="G23" s="18">
         <v>781242</v>
@@ -1488,7 +1488,7 @@
       <c r="I23" s="19"/>
       <c r="J23" s="20"/>
     </row>
-    <row r="24" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B24" s="15" t="s">
         <v>8</v>
       </c>
@@ -1499,10 +1499,10 @@
         <v>10</v>
       </c>
       <c r="E24" s="16" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F24" s="18">
-        <v>27578</v>
+        <v>31249</v>
       </c>
       <c r="G24" s="18">
         <v>781242</v>
@@ -1511,21 +1511,21 @@
       <c r="I24" s="19"/>
       <c r="J24" s="20"/>
     </row>
-    <row r="25" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B25" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C25" s="16" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D25" s="17" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E25" s="16" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F25" s="18">
-        <v>27578</v>
+        <v>31249</v>
       </c>
       <c r="G25" s="18">
         <v>781242</v>
@@ -1534,7 +1534,7 @@
       <c r="I25" s="19"/>
       <c r="J25" s="20"/>
     </row>
-    <row r="26" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B26" s="15" t="s">
         <v>8</v>
       </c>
@@ -1545,10 +1545,10 @@
         <v>10</v>
       </c>
       <c r="E26" s="16" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F26" s="18">
-        <v>27578</v>
+        <v>31249</v>
       </c>
       <c r="G26" s="18">
         <v>781242</v>
@@ -1557,21 +1557,21 @@
       <c r="I26" s="19"/>
       <c r="J26" s="20"/>
     </row>
-    <row r="27" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B27" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C27" s="16" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D27" s="17" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E27" s="16" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F27" s="18">
-        <v>27578</v>
+        <v>31249</v>
       </c>
       <c r="G27" s="18">
         <v>781242</v>
@@ -1580,7 +1580,7 @@
       <c r="I27" s="19"/>
       <c r="J27" s="20"/>
     </row>
-    <row r="28" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B28" s="15" t="s">
         <v>8</v>
       </c>
@@ -1591,10 +1591,10 @@
         <v>10</v>
       </c>
       <c r="E28" s="16" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F28" s="18">
-        <v>27578</v>
+        <v>31249</v>
       </c>
       <c r="G28" s="18">
         <v>781242</v>
@@ -1603,7 +1603,7 @@
       <c r="I28" s="19"/>
       <c r="J28" s="20"/>
     </row>
-    <row r="29" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B29" s="15" t="s">
         <v>8</v>
       </c>
@@ -1614,10 +1614,10 @@
         <v>10</v>
       </c>
       <c r="E29" s="16" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F29" s="18">
-        <v>27578</v>
+        <v>31249</v>
       </c>
       <c r="G29" s="18">
         <v>781242</v>
@@ -1626,21 +1626,21 @@
       <c r="I29" s="19"/>
       <c r="J29" s="20"/>
     </row>
-    <row r="30" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B30" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C30" s="16" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D30" s="17" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E30" s="16" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F30" s="18">
-        <v>27578</v>
+        <v>31249</v>
       </c>
       <c r="G30" s="18">
         <v>781242</v>
@@ -1649,7 +1649,7 @@
       <c r="I30" s="19"/>
       <c r="J30" s="20"/>
     </row>
-    <row r="31" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B31" s="15" t="s">
         <v>8</v>
       </c>
@@ -1660,10 +1660,10 @@
         <v>10</v>
       </c>
       <c r="E31" s="16" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="F31" s="18">
-        <v>27578</v>
+        <v>31249</v>
       </c>
       <c r="G31" s="18">
         <v>781242</v>
@@ -1672,21 +1672,21 @@
       <c r="I31" s="19"/>
       <c r="J31" s="20"/>
     </row>
-    <row r="32" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B32" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C32" s="16" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D32" s="17" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E32" s="16" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="F32" s="18">
-        <v>27578</v>
+        <v>31249</v>
       </c>
       <c r="G32" s="18">
         <v>781242</v>
@@ -1695,7 +1695,7 @@
       <c r="I32" s="19"/>
       <c r="J32" s="20"/>
     </row>
-    <row r="33" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B33" s="15" t="s">
         <v>8</v>
       </c>
@@ -1706,10 +1706,10 @@
         <v>10</v>
       </c>
       <c r="E33" s="16" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="F33" s="18">
-        <v>27578</v>
+        <v>31249</v>
       </c>
       <c r="G33" s="18">
         <v>781242</v>
@@ -1718,21 +1718,21 @@
       <c r="I33" s="19"/>
       <c r="J33" s="20"/>
     </row>
-    <row r="34" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B34" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C34" s="16" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D34" s="17" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E34" s="16" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="F34" s="18">
-        <v>27578</v>
+        <v>31249</v>
       </c>
       <c r="G34" s="18">
         <v>781242</v>
@@ -1741,7 +1741,7 @@
       <c r="I34" s="19"/>
       <c r="J34" s="20"/>
     </row>
-    <row r="35" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B35" s="15" t="s">
         <v>8</v>
       </c>
@@ -1752,10 +1752,10 @@
         <v>10</v>
       </c>
       <c r="E35" s="16" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="F35" s="18">
-        <v>27578</v>
+        <v>31249</v>
       </c>
       <c r="G35" s="18">
         <v>781242</v>
@@ -1764,21 +1764,21 @@
       <c r="I35" s="19"/>
       <c r="J35" s="20"/>
     </row>
-    <row r="36" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B36" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C36" s="16" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D36" s="17" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E36" s="16" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="F36" s="18">
-        <v>27578</v>
+        <v>31249</v>
       </c>
       <c r="G36" s="18">
         <v>781242</v>
@@ -1787,7 +1787,7 @@
       <c r="I36" s="19"/>
       <c r="J36" s="20"/>
     </row>
-    <row r="37" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B37" s="15" t="s">
         <v>8</v>
       </c>
@@ -1798,10 +1798,10 @@
         <v>10</v>
       </c>
       <c r="E37" s="16" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="F37" s="18">
-        <v>27578</v>
+        <v>31249</v>
       </c>
       <c r="G37" s="18">
         <v>781242</v>
@@ -1810,21 +1810,21 @@
       <c r="I37" s="19"/>
       <c r="J37" s="20"/>
     </row>
-    <row r="38" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B38" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C38" s="16" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D38" s="17" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E38" s="16" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="F38" s="18">
-        <v>27578</v>
+        <v>31249</v>
       </c>
       <c r="G38" s="18">
         <v>781242</v>
@@ -1833,7 +1833,7 @@
       <c r="I38" s="19"/>
       <c r="J38" s="20"/>
     </row>
-    <row r="39" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B39" s="15" t="s">
         <v>8</v>
       </c>
@@ -1844,10 +1844,10 @@
         <v>10</v>
       </c>
       <c r="E39" s="16" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="F39" s="18">
-        <v>27578</v>
+        <v>31249</v>
       </c>
       <c r="G39" s="18">
         <v>781242</v>
@@ -1856,21 +1856,21 @@
       <c r="I39" s="19"/>
       <c r="J39" s="20"/>
     </row>
-    <row r="40" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B40" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C40" s="16" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D40" s="17" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E40" s="16" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="F40" s="18">
-        <v>27578</v>
+        <v>31249</v>
       </c>
       <c r="G40" s="18">
         <v>781242</v>
@@ -1879,7 +1879,7 @@
       <c r="I40" s="19"/>
       <c r="J40" s="20"/>
     </row>
-    <row r="41" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="41" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B41" s="15" t="s">
         <v>8</v>
       </c>
@@ -1890,10 +1890,10 @@
         <v>10</v>
       </c>
       <c r="E41" s="16" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="F41" s="18">
-        <v>27578</v>
+        <v>31249</v>
       </c>
       <c r="G41" s="18">
         <v>781242</v>
@@ -1902,21 +1902,21 @@
       <c r="I41" s="19"/>
       <c r="J41" s="20"/>
     </row>
-    <row r="42" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="42" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B42" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C42" s="16" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D42" s="17" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E42" s="16" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="F42" s="18">
-        <v>27578</v>
+        <v>31249</v>
       </c>
       <c r="G42" s="18">
         <v>781242</v>
@@ -1925,7 +1925,7 @@
       <c r="I42" s="19"/>
       <c r="J42" s="20"/>
     </row>
-    <row r="43" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="43" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B43" s="15" t="s">
         <v>8</v>
       </c>
@@ -1936,10 +1936,10 @@
         <v>10</v>
       </c>
       <c r="E43" s="16" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="F43" s="18">
-        <v>27578</v>
+        <v>31249</v>
       </c>
       <c r="G43" s="18">
         <v>781242</v>
@@ -1948,21 +1948,21 @@
       <c r="I43" s="19"/>
       <c r="J43" s="20"/>
     </row>
-    <row r="44" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="44" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B44" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C44" s="16" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D44" s="17" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E44" s="16" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="F44" s="18">
-        <v>27578</v>
+        <v>31249</v>
       </c>
       <c r="G44" s="18">
         <v>781242</v>
@@ -1971,7 +1971,7 @@
       <c r="I44" s="19"/>
       <c r="J44" s="20"/>
     </row>
-    <row r="45" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="45" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B45" s="15" t="s">
         <v>8</v>
       </c>
@@ -1982,10 +1982,10 @@
         <v>10</v>
       </c>
       <c r="E45" s="16" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="F45" s="18">
-        <v>27578</v>
+        <v>31249</v>
       </c>
       <c r="G45" s="18">
         <v>781242</v>
@@ -1994,21 +1994,21 @@
       <c r="I45" s="19"/>
       <c r="J45" s="20"/>
     </row>
-    <row r="46" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="46" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B46" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C46" s="16" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D46" s="17" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E46" s="16" t="s">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="F46" s="18">
-        <v>27578</v>
+        <v>31249</v>
       </c>
       <c r="G46" s="18">
         <v>781242</v>
@@ -2017,7 +2017,7 @@
       <c r="I46" s="19"/>
       <c r="J46" s="20"/>
     </row>
-    <row r="47" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="47" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B47" s="15" t="s">
         <v>8</v>
       </c>
@@ -2028,10 +2028,10 @@
         <v>10</v>
       </c>
       <c r="E47" s="16" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="F47" s="18">
-        <v>27578</v>
+        <v>31249</v>
       </c>
       <c r="G47" s="18">
         <v>781242</v>
@@ -2040,21 +2040,21 @@
       <c r="I47" s="19"/>
       <c r="J47" s="20"/>
     </row>
-    <row r="48" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="48" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B48" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C48" s="16" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D48" s="17" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E48" s="16" t="s">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="F48" s="18">
-        <v>27578</v>
+        <v>31249</v>
       </c>
       <c r="G48" s="18">
         <v>781242</v>
@@ -2063,7 +2063,7 @@
       <c r="I48" s="19"/>
       <c r="J48" s="20"/>
     </row>
-    <row r="49" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="49" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B49" s="15" t="s">
         <v>8</v>
       </c>
@@ -2074,10 +2074,10 @@
         <v>10</v>
       </c>
       <c r="E49" s="16" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="F49" s="18">
-        <v>27578</v>
+        <v>31249</v>
       </c>
       <c r="G49" s="18">
         <v>781242</v>
@@ -2086,21 +2086,21 @@
       <c r="I49" s="19"/>
       <c r="J49" s="20"/>
     </row>
-    <row r="50" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="50" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B50" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C50" s="16" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D50" s="17" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E50" s="16" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="F50" s="18">
-        <v>27578</v>
+        <v>31249</v>
       </c>
       <c r="G50" s="18">
         <v>781242</v>
@@ -2109,7 +2109,7 @@
       <c r="I50" s="19"/>
       <c r="J50" s="20"/>
     </row>
-    <row r="51" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="51" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B51" s="15" t="s">
         <v>8</v>
       </c>
@@ -2120,10 +2120,10 @@
         <v>10</v>
       </c>
       <c r="E51" s="16" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="F51" s="18">
-        <v>27578</v>
+        <v>31249</v>
       </c>
       <c r="G51" s="18">
         <v>781242</v>
@@ -2132,21 +2132,21 @@
       <c r="I51" s="19"/>
       <c r="J51" s="20"/>
     </row>
-    <row r="52" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="52" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B52" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C52" s="16" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D52" s="17" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E52" s="16" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="F52" s="18">
-        <v>27578</v>
+        <v>31249</v>
       </c>
       <c r="G52" s="18">
         <v>781242</v>
@@ -2155,7 +2155,7 @@
       <c r="I52" s="19"/>
       <c r="J52" s="20"/>
     </row>
-    <row r="53" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="53" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B53" s="15" t="s">
         <v>8</v>
       </c>
@@ -2166,10 +2166,10 @@
         <v>10</v>
       </c>
       <c r="E53" s="16" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="F53" s="18">
-        <v>27578</v>
+        <v>31249</v>
       </c>
       <c r="G53" s="18">
         <v>781242</v>
@@ -2178,21 +2178,21 @@
       <c r="I53" s="19"/>
       <c r="J53" s="20"/>
     </row>
-    <row r="54" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="54" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B54" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C54" s="16" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D54" s="17" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E54" s="16" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="F54" s="18">
-        <v>27578</v>
+        <v>31249</v>
       </c>
       <c r="G54" s="18">
         <v>781242</v>
@@ -2201,7 +2201,7 @@
       <c r="I54" s="19"/>
       <c r="J54" s="20"/>
     </row>
-    <row r="55" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="55" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B55" s="15" t="s">
         <v>8</v>
       </c>
@@ -2212,10 +2212,10 @@
         <v>10</v>
       </c>
       <c r="E55" s="16" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="F55" s="18">
-        <v>27578</v>
+        <v>31249</v>
       </c>
       <c r="G55" s="18">
         <v>781242</v>
@@ -2224,21 +2224,21 @@
       <c r="I55" s="19"/>
       <c r="J55" s="20"/>
     </row>
-    <row r="56" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="56" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B56" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C56" s="16" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D56" s="17" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E56" s="16" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="F56" s="18">
-        <v>27578</v>
+        <v>31249</v>
       </c>
       <c r="G56" s="18">
         <v>781242</v>
@@ -2247,7 +2247,7 @@
       <c r="I56" s="19"/>
       <c r="J56" s="20"/>
     </row>
-    <row r="57" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="57" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B57" s="15" t="s">
         <v>8</v>
       </c>
@@ -2258,10 +2258,10 @@
         <v>10</v>
       </c>
       <c r="E57" s="16" t="s">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="F57" s="18">
-        <v>27578</v>
+        <v>31249</v>
       </c>
       <c r="G57" s="18">
         <v>781242</v>
@@ -2270,21 +2270,21 @@
       <c r="I57" s="19"/>
       <c r="J57" s="20"/>
     </row>
-    <row r="58" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="58" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B58" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C58" s="16" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D58" s="17" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E58" s="16" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="F58" s="18">
-        <v>27578</v>
+        <v>31249</v>
       </c>
       <c r="G58" s="18">
         <v>781242</v>
@@ -2293,7 +2293,7 @@
       <c r="I58" s="19"/>
       <c r="J58" s="20"/>
     </row>
-    <row r="59" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="59" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B59" s="15" t="s">
         <v>8</v>
       </c>
@@ -2304,10 +2304,10 @@
         <v>10</v>
       </c>
       <c r="E59" s="16" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="F59" s="18">
-        <v>27578</v>
+        <v>31249</v>
       </c>
       <c r="G59" s="18">
         <v>781242</v>
@@ -2316,21 +2316,21 @@
       <c r="I59" s="19"/>
       <c r="J59" s="20"/>
     </row>
-    <row r="60" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="60" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B60" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C60" s="16" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D60" s="17" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E60" s="16" t="s">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="F60" s="18">
-        <v>27578</v>
+        <v>31249</v>
       </c>
       <c r="G60" s="18">
         <v>781242</v>
@@ -2339,7 +2339,7 @@
       <c r="I60" s="19"/>
       <c r="J60" s="20"/>
     </row>
-    <row r="61" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="61" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B61" s="15" t="s">
         <v>8</v>
       </c>
@@ -2350,10 +2350,10 @@
         <v>10</v>
       </c>
       <c r="E61" s="16" t="s">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="F61" s="18">
-        <v>27578</v>
+        <v>31249</v>
       </c>
       <c r="G61" s="18">
         <v>781242</v>
@@ -2362,21 +2362,21 @@
       <c r="I61" s="19"/>
       <c r="J61" s="20"/>
     </row>
-    <row r="62" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="62" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B62" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C62" s="16" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D62" s="17" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E62" s="16" t="s">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="F62" s="18">
-        <v>27578</v>
+        <v>31249</v>
       </c>
       <c r="G62" s="18">
         <v>781242</v>
@@ -2385,7 +2385,7 @@
       <c r="I62" s="19"/>
       <c r="J62" s="20"/>
     </row>
-    <row r="63" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="63" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B63" s="15" t="s">
         <v>8</v>
       </c>
@@ -2396,7 +2396,7 @@
         <v>10</v>
       </c>
       <c r="E63" s="16" t="s">
-        <v>37</v>
+        <v>58</v>
       </c>
       <c r="F63" s="18">
         <v>31249</v>
@@ -2408,18 +2408,18 @@
       <c r="I63" s="19"/>
       <c r="J63" s="20"/>
     </row>
-    <row r="64" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="64" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B64" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C64" s="16" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D64" s="17" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E64" s="16" t="s">
-        <v>37</v>
+        <v>59</v>
       </c>
       <c r="F64" s="18">
         <v>31249</v>
@@ -2431,7 +2431,7 @@
       <c r="I64" s="19"/>
       <c r="J64" s="20"/>
     </row>
-    <row r="65" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="65" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B65" s="15" t="s">
         <v>8</v>
       </c>
@@ -2442,7 +2442,7 @@
         <v>10</v>
       </c>
       <c r="E65" s="16" t="s">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="F65" s="18">
         <v>31249</v>
@@ -2454,18 +2454,18 @@
       <c r="I65" s="19"/>
       <c r="J65" s="20"/>
     </row>
-    <row r="66" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="66" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B66" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C66" s="16" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D66" s="17" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E66" s="16" t="s">
-        <v>38</v>
+        <v>61</v>
       </c>
       <c r="F66" s="18">
         <v>31249</v>
@@ -2477,7 +2477,7 @@
       <c r="I66" s="19"/>
       <c r="J66" s="20"/>
     </row>
-    <row r="67" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="67" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B67" s="15" t="s">
         <v>8</v>
       </c>
@@ -2488,7 +2488,7 @@
         <v>10</v>
       </c>
       <c r="E67" s="16" t="s">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="F67" s="18">
         <v>31249</v>
@@ -2500,18 +2500,18 @@
       <c r="I67" s="19"/>
       <c r="J67" s="20"/>
     </row>
-    <row r="68" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="68" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B68" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C68" s="16" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D68" s="17" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E68" s="16" t="s">
-        <v>39</v>
+        <v>63</v>
       </c>
       <c r="F68" s="18">
         <v>31249</v>
@@ -2523,7 +2523,7 @@
       <c r="I68" s="19"/>
       <c r="J68" s="20"/>
     </row>
-    <row r="69" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="69" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B69" s="15" t="s">
         <v>8</v>
       </c>
@@ -2534,7 +2534,7 @@
         <v>10</v>
       </c>
       <c r="E69" s="16" t="s">
-        <v>40</v>
+        <v>64</v>
       </c>
       <c r="F69" s="18">
         <v>31249</v>
@@ -2546,18 +2546,18 @@
       <c r="I69" s="19"/>
       <c r="J69" s="20"/>
     </row>
-    <row r="70" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="70" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B70" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C70" s="16" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D70" s="17" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E70" s="16" t="s">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="F70" s="18">
         <v>31249</v>
@@ -2569,7 +2569,7 @@
       <c r="I70" s="19"/>
       <c r="J70" s="20"/>
     </row>
-    <row r="71" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="71" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B71" s="15" t="s">
         <v>8</v>
       </c>
@@ -2580,7 +2580,7 @@
         <v>10</v>
       </c>
       <c r="E71" s="16" t="s">
-        <v>41</v>
+        <v>66</v>
       </c>
       <c r="F71" s="18">
         <v>31249</v>
@@ -2592,18 +2592,18 @@
       <c r="I71" s="19"/>
       <c r="J71" s="20"/>
     </row>
-    <row r="72" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="72" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B72" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C72" s="16" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D72" s="17" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E72" s="16" t="s">
-        <v>41</v>
+        <v>67</v>
       </c>
       <c r="F72" s="18">
         <v>31249</v>
@@ -2615,7 +2615,7 @@
       <c r="I72" s="19"/>
       <c r="J72" s="20"/>
     </row>
-    <row r="73" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="73" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B73" s="15" t="s">
         <v>8</v>
       </c>
@@ -2626,7 +2626,7 @@
         <v>10</v>
       </c>
       <c r="E73" s="16" t="s">
-        <v>42</v>
+        <v>68</v>
       </c>
       <c r="F73" s="18">
         <v>31249</v>
@@ -2638,18 +2638,18 @@
       <c r="I73" s="19"/>
       <c r="J73" s="20"/>
     </row>
-    <row r="74" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="74" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B74" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C74" s="16" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D74" s="17" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E74" s="16" t="s">
-        <v>42</v>
+        <v>69</v>
       </c>
       <c r="F74" s="18">
         <v>31249</v>
@@ -2661,7 +2661,7 @@
       <c r="I74" s="19"/>
       <c r="J74" s="20"/>
     </row>
-    <row r="75" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="75" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B75" s="15" t="s">
         <v>8</v>
       </c>
@@ -2672,7 +2672,7 @@
         <v>10</v>
       </c>
       <c r="E75" s="16" t="s">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="F75" s="18">
         <v>31249</v>
@@ -2684,18 +2684,18 @@
       <c r="I75" s="19"/>
       <c r="J75" s="20"/>
     </row>
-    <row r="76" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="76" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B76" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C76" s="16" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D76" s="17" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E76" s="16" t="s">
-        <v>43</v>
+        <v>71</v>
       </c>
       <c r="F76" s="18">
         <v>31249</v>
@@ -2707,7 +2707,7 @@
       <c r="I76" s="19"/>
       <c r="J76" s="20"/>
     </row>
-    <row r="77" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="77" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B77" s="15" t="s">
         <v>8</v>
       </c>
@@ -2718,7 +2718,7 @@
         <v>10</v>
       </c>
       <c r="E77" s="16" t="s">
-        <v>44</v>
+        <v>72</v>
       </c>
       <c r="F77" s="18">
         <v>31249</v>
@@ -2730,18 +2730,18 @@
       <c r="I77" s="19"/>
       <c r="J77" s="20"/>
     </row>
-    <row r="78" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="78" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B78" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C78" s="16" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D78" s="17" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E78" s="16" t="s">
-        <v>44</v>
+        <v>73</v>
       </c>
       <c r="F78" s="18">
         <v>31249</v>
@@ -2753,7 +2753,7 @@
       <c r="I78" s="19"/>
       <c r="J78" s="20"/>
     </row>
-    <row r="79" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="79" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B79" s="15" t="s">
         <v>8</v>
       </c>
@@ -2764,7 +2764,7 @@
         <v>10</v>
       </c>
       <c r="E79" s="16" t="s">
-        <v>45</v>
+        <v>74</v>
       </c>
       <c r="F79" s="18">
         <v>31249</v>
@@ -2776,18 +2776,18 @@
       <c r="I79" s="19"/>
       <c r="J79" s="20"/>
     </row>
-    <row r="80" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="80" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B80" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C80" s="16" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D80" s="17" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E80" s="16" t="s">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="F80" s="18">
         <v>31249</v>
@@ -2799,7 +2799,7 @@
       <c r="I80" s="19"/>
       <c r="J80" s="20"/>
     </row>
-    <row r="81" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="81" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B81" s="15" t="s">
         <v>8</v>
       </c>
@@ -2810,7 +2810,7 @@
         <v>10</v>
       </c>
       <c r="E81" s="16" t="s">
-        <v>46</v>
+        <v>76</v>
       </c>
       <c r="F81" s="18">
         <v>31249</v>
@@ -2822,18 +2822,18 @@
       <c r="I81" s="19"/>
       <c r="J81" s="20"/>
     </row>
-    <row r="82" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="82" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B82" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C82" s="16" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D82" s="17" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E82" s="16" t="s">
-        <v>46</v>
+        <v>77</v>
       </c>
       <c r="F82" s="18">
         <v>31249</v>
@@ -2845,7 +2845,7 @@
       <c r="I82" s="19"/>
       <c r="J82" s="20"/>
     </row>
-    <row r="83" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="83" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B83" s="15" t="s">
         <v>8</v>
       </c>
@@ -2856,7 +2856,7 @@
         <v>10</v>
       </c>
       <c r="E83" s="16" t="s">
-        <v>47</v>
+        <v>78</v>
       </c>
       <c r="F83" s="18">
         <v>31249</v>
@@ -2868,18 +2868,18 @@
       <c r="I83" s="19"/>
       <c r="J83" s="20"/>
     </row>
-    <row r="84" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="84" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B84" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C84" s="16" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D84" s="17" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E84" s="16" t="s">
-        <v>47</v>
+        <v>79</v>
       </c>
       <c r="F84" s="18">
         <v>31249</v>
@@ -2891,7 +2891,7 @@
       <c r="I84" s="19"/>
       <c r="J84" s="20"/>
     </row>
-    <row r="85" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="85" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B85" s="15" t="s">
         <v>8</v>
       </c>
@@ -2902,7 +2902,7 @@
         <v>10</v>
       </c>
       <c r="E85" s="16" t="s">
-        <v>48</v>
+        <v>80</v>
       </c>
       <c r="F85" s="18">
         <v>31249</v>
@@ -2914,18 +2914,18 @@
       <c r="I85" s="19"/>
       <c r="J85" s="20"/>
     </row>
-    <row r="86" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="86" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B86" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C86" s="16" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D86" s="17" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E86" s="16" t="s">
-        <v>48</v>
+        <v>81</v>
       </c>
       <c r="F86" s="18">
         <v>31249</v>
@@ -2937,7 +2937,7 @@
       <c r="I86" s="19"/>
       <c r="J86" s="20"/>
     </row>
-    <row r="87" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="87" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B87" s="15" t="s">
         <v>8</v>
       </c>
@@ -2948,7 +2948,7 @@
         <v>10</v>
       </c>
       <c r="E87" s="16" t="s">
-        <v>49</v>
+        <v>82</v>
       </c>
       <c r="F87" s="18">
         <v>31249</v>
@@ -2960,18 +2960,18 @@
       <c r="I87" s="19"/>
       <c r="J87" s="20"/>
     </row>
-    <row r="88" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="88" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B88" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C88" s="16" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D88" s="17" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E88" s="16" t="s">
-        <v>49</v>
+        <v>83</v>
       </c>
       <c r="F88" s="18">
         <v>31249</v>
@@ -2983,7 +2983,7 @@
       <c r="I88" s="19"/>
       <c r="J88" s="20"/>
     </row>
-    <row r="89" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="89" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B89" s="15" t="s">
         <v>8</v>
       </c>
@@ -2994,7 +2994,7 @@
         <v>10</v>
       </c>
       <c r="E89" s="16" t="s">
-        <v>50</v>
+        <v>84</v>
       </c>
       <c r="F89" s="18">
         <v>31249</v>
@@ -3006,18 +3006,18 @@
       <c r="I89" s="19"/>
       <c r="J89" s="20"/>
     </row>
-    <row r="90" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="90" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B90" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C90" s="16" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D90" s="17" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E90" s="16" t="s">
-        <v>50</v>
+        <v>85</v>
       </c>
       <c r="F90" s="18">
         <v>31249</v>
@@ -3029,7 +3029,7 @@
       <c r="I90" s="19"/>
       <c r="J90" s="20"/>
     </row>
-    <row r="91" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="91" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B91" s="15" t="s">
         <v>8</v>
       </c>
@@ -3040,7 +3040,7 @@
         <v>10</v>
       </c>
       <c r="E91" s="16" t="s">
-        <v>51</v>
+        <v>86</v>
       </c>
       <c r="F91" s="18">
         <v>31249</v>
@@ -3052,18 +3052,18 @@
       <c r="I91" s="19"/>
       <c r="J91" s="20"/>
     </row>
-    <row r="92" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="92" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B92" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C92" s="16" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D92" s="17" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E92" s="16" t="s">
-        <v>51</v>
+        <v>87</v>
       </c>
       <c r="F92" s="18">
         <v>31249</v>
@@ -3075,7 +3075,7 @@
       <c r="I92" s="19"/>
       <c r="J92" s="20"/>
     </row>
-    <row r="93" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="93" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B93" s="15" t="s">
         <v>8</v>
       </c>
@@ -3086,7 +3086,7 @@
         <v>10</v>
       </c>
       <c r="E93" s="16" t="s">
-        <v>52</v>
+        <v>88</v>
       </c>
       <c r="F93" s="18">
         <v>31249</v>
@@ -3098,21 +3098,21 @@
       <c r="I93" s="19"/>
       <c r="J93" s="20"/>
     </row>
-    <row r="94" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="94" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B94" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C94" s="16" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D94" s="17" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E94" s="16" t="s">
-        <v>52</v>
+        <v>89</v>
       </c>
       <c r="F94" s="18">
-        <v>31249</v>
+        <v>27578</v>
       </c>
       <c r="G94" s="18">
         <v>781242</v>
@@ -3121,7 +3121,7 @@
       <c r="I94" s="19"/>
       <c r="J94" s="20"/>
     </row>
-    <row r="95" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="95" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B95" s="15" t="s">
         <v>8</v>
       </c>
@@ -3132,10 +3132,10 @@
         <v>10</v>
       </c>
       <c r="E95" s="16" t="s">
-        <v>53</v>
+        <v>90</v>
       </c>
       <c r="F95" s="18">
-        <v>31249</v>
+        <v>27578</v>
       </c>
       <c r="G95" s="18">
         <v>781242</v>
@@ -3144,21 +3144,21 @@
       <c r="I95" s="19"/>
       <c r="J95" s="20"/>
     </row>
-    <row r="96" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="96" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B96" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C96" s="16" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D96" s="17" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E96" s="16" t="s">
-        <v>53</v>
+        <v>91</v>
       </c>
       <c r="F96" s="18">
-        <v>31249</v>
+        <v>27578</v>
       </c>
       <c r="G96" s="18">
         <v>781242</v>
@@ -3167,7 +3167,7 @@
       <c r="I96" s="19"/>
       <c r="J96" s="20"/>
     </row>
-    <row r="97" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="97" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B97" s="15" t="s">
         <v>8</v>
       </c>
@@ -3178,10 +3178,10 @@
         <v>10</v>
       </c>
       <c r="E97" s="16" t="s">
-        <v>54</v>
+        <v>92</v>
       </c>
       <c r="F97" s="18">
-        <v>31249</v>
+        <v>27578</v>
       </c>
       <c r="G97" s="18">
         <v>781242</v>
@@ -3190,21 +3190,21 @@
       <c r="I97" s="19"/>
       <c r="J97" s="20"/>
     </row>
-    <row r="98" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="98" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B98" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C98" s="16" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D98" s="17" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E98" s="16" t="s">
-        <v>54</v>
+        <v>93</v>
       </c>
       <c r="F98" s="18">
-        <v>31249</v>
+        <v>27578</v>
       </c>
       <c r="G98" s="18">
         <v>781242</v>
@@ -3213,7 +3213,7 @@
       <c r="I98" s="19"/>
       <c r="J98" s="20"/>
     </row>
-    <row r="99" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="99" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B99" s="15" t="s">
         <v>8</v>
       </c>
@@ -3224,10 +3224,10 @@
         <v>10</v>
       </c>
       <c r="E99" s="16" t="s">
-        <v>55</v>
+        <v>94</v>
       </c>
       <c r="F99" s="18">
-        <v>31249</v>
+        <v>27578</v>
       </c>
       <c r="G99" s="18">
         <v>781242</v>
@@ -3236,21 +3236,21 @@
       <c r="I99" s="19"/>
       <c r="J99" s="20"/>
     </row>
-    <row r="100" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="100" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B100" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C100" s="16" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D100" s="17" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E100" s="16" t="s">
-        <v>55</v>
+        <v>95</v>
       </c>
       <c r="F100" s="18">
-        <v>31249</v>
+        <v>27578</v>
       </c>
       <c r="G100" s="18">
         <v>781242</v>
@@ -3259,7 +3259,7 @@
       <c r="I100" s="19"/>
       <c r="J100" s="20"/>
     </row>
-    <row r="101" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="101" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B101" s="15" t="s">
         <v>8</v>
       </c>
@@ -3270,10 +3270,10 @@
         <v>10</v>
       </c>
       <c r="E101" s="16" t="s">
-        <v>56</v>
+        <v>96</v>
       </c>
       <c r="F101" s="18">
-        <v>31249</v>
+        <v>27578</v>
       </c>
       <c r="G101" s="18">
         <v>781242</v>
@@ -3282,21 +3282,21 @@
       <c r="I101" s="19"/>
       <c r="J101" s="20"/>
     </row>
-    <row r="102" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="102" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B102" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C102" s="16" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D102" s="17" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E102" s="16" t="s">
-        <v>56</v>
+        <v>97</v>
       </c>
       <c r="F102" s="18">
-        <v>31249</v>
+        <v>27578</v>
       </c>
       <c r="G102" s="18">
         <v>781242</v>
@@ -3305,7 +3305,7 @@
       <c r="I102" s="19"/>
       <c r="J102" s="20"/>
     </row>
-    <row r="103" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="103" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B103" s="15" t="s">
         <v>8</v>
       </c>
@@ -3316,10 +3316,10 @@
         <v>10</v>
       </c>
       <c r="E103" s="16" t="s">
-        <v>57</v>
+        <v>98</v>
       </c>
       <c r="F103" s="18">
-        <v>31249</v>
+        <v>27578</v>
       </c>
       <c r="G103" s="18">
         <v>781242</v>
@@ -3328,21 +3328,21 @@
       <c r="I103" s="19"/>
       <c r="J103" s="20"/>
     </row>
-    <row r="104" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="104" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B104" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C104" s="16" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D104" s="17" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E104" s="16" t="s">
-        <v>57</v>
+        <v>99</v>
       </c>
       <c r="F104" s="18">
-        <v>31249</v>
+        <v>27578</v>
       </c>
       <c r="G104" s="18">
         <v>781242</v>
@@ -3351,7 +3351,7 @@
       <c r="I104" s="19"/>
       <c r="J104" s="20"/>
     </row>
-    <row r="105" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="105" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B105" s="15" t="s">
         <v>8</v>
       </c>
@@ -3362,10 +3362,10 @@
         <v>10</v>
       </c>
       <c r="E105" s="16" t="s">
-        <v>58</v>
+        <v>100</v>
       </c>
       <c r="F105" s="18">
-        <v>31249</v>
+        <v>27578</v>
       </c>
       <c r="G105" s="18">
         <v>781242</v>
@@ -3374,21 +3374,21 @@
       <c r="I105" s="19"/>
       <c r="J105" s="20"/>
     </row>
-    <row r="106" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="106" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B106" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C106" s="16" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D106" s="17" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E106" s="16" t="s">
-        <v>58</v>
+        <v>101</v>
       </c>
       <c r="F106" s="18">
-        <v>31249</v>
+        <v>27578</v>
       </c>
       <c r="G106" s="18">
         <v>781242</v>
@@ -3397,7 +3397,7 @@
       <c r="I106" s="19"/>
       <c r="J106" s="20"/>
     </row>
-    <row r="107" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="107" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B107" s="15" t="s">
         <v>8</v>
       </c>
@@ -3408,10 +3408,10 @@
         <v>10</v>
       </c>
       <c r="E107" s="16" t="s">
-        <v>59</v>
+        <v>102</v>
       </c>
       <c r="F107" s="18">
-        <v>31249</v>
+        <v>27578</v>
       </c>
       <c r="G107" s="18">
         <v>781242</v>
@@ -3420,21 +3420,21 @@
       <c r="I107" s="19"/>
       <c r="J107" s="20"/>
     </row>
-    <row r="108" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="108" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B108" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C108" s="16" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D108" s="17" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E108" s="16" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="F108" s="18">
-        <v>31249</v>
+        <v>27578</v>
       </c>
       <c r="G108" s="18">
         <v>781242</v>
@@ -3443,7 +3443,7 @@
       <c r="I108" s="19"/>
       <c r="J108" s="20"/>
     </row>
-    <row r="109" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="109" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B109" s="15" t="s">
         <v>8</v>
       </c>
@@ -3454,10 +3454,10 @@
         <v>10</v>
       </c>
       <c r="E109" s="16" t="s">
-        <v>60</v>
+        <v>104</v>
       </c>
       <c r="F109" s="18">
-        <v>31249</v>
+        <v>27578</v>
       </c>
       <c r="G109" s="18">
         <v>781242</v>
@@ -3466,21 +3466,21 @@
       <c r="I109" s="19"/>
       <c r="J109" s="20"/>
     </row>
-    <row r="110" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="110" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B110" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C110" s="16" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D110" s="17" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E110" s="16" t="s">
-        <v>60</v>
+        <v>105</v>
       </c>
       <c r="F110" s="18">
-        <v>31249</v>
+        <v>27578</v>
       </c>
       <c r="G110" s="18">
         <v>781242</v>
@@ -3489,7 +3489,7 @@
       <c r="I110" s="19"/>
       <c r="J110" s="20"/>
     </row>
-    <row r="111" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="111" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B111" s="15" t="s">
         <v>8</v>
       </c>
@@ -3500,10 +3500,10 @@
         <v>10</v>
       </c>
       <c r="E111" s="16" t="s">
-        <v>61</v>
+        <v>106</v>
       </c>
       <c r="F111" s="18">
-        <v>31249</v>
+        <v>27578</v>
       </c>
       <c r="G111" s="18">
         <v>781242</v>
@@ -3512,21 +3512,21 @@
       <c r="I111" s="19"/>
       <c r="J111" s="20"/>
     </row>
-    <row r="112" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="112" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B112" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C112" s="16" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D112" s="17" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E112" s="16" t="s">
-        <v>61</v>
+        <v>107</v>
       </c>
       <c r="F112" s="18">
-        <v>31249</v>
+        <v>27578</v>
       </c>
       <c r="G112" s="18">
         <v>781242</v>
@@ -3535,7 +3535,7 @@
       <c r="I112" s="19"/>
       <c r="J112" s="20"/>
     </row>
-    <row r="113" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="113" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B113" s="15" t="s">
         <v>8</v>
       </c>
@@ -3546,10 +3546,10 @@
         <v>10</v>
       </c>
       <c r="E113" s="16" t="s">
-        <v>62</v>
+        <v>108</v>
       </c>
       <c r="F113" s="18">
-        <v>31249</v>
+        <v>27578</v>
       </c>
       <c r="G113" s="18">
         <v>781242</v>
@@ -3558,21 +3558,21 @@
       <c r="I113" s="19"/>
       <c r="J113" s="20"/>
     </row>
-    <row r="114" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="114" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B114" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C114" s="16" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D114" s="17" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E114" s="16" t="s">
-        <v>62</v>
+        <v>109</v>
       </c>
       <c r="F114" s="18">
-        <v>31249</v>
+        <v>27578</v>
       </c>
       <c r="G114" s="18">
         <v>781242</v>
@@ -3581,7 +3581,7 @@
       <c r="I114" s="19"/>
       <c r="J114" s="20"/>
     </row>
-    <row r="115" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="115" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B115" s="15" t="s">
         <v>8</v>
       </c>
@@ -3592,10 +3592,10 @@
         <v>10</v>
       </c>
       <c r="E115" s="16" t="s">
-        <v>63</v>
+        <v>110</v>
       </c>
       <c r="F115" s="18">
-        <v>31249</v>
+        <v>27578</v>
       </c>
       <c r="G115" s="18">
         <v>781242</v>
@@ -3604,21 +3604,21 @@
       <c r="I115" s="19"/>
       <c r="J115" s="20"/>
     </row>
-    <row r="116" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="116" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B116" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C116" s="16" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D116" s="17" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E116" s="16" t="s">
-        <v>63</v>
+        <v>111</v>
       </c>
       <c r="F116" s="18">
-        <v>31249</v>
+        <v>27578</v>
       </c>
       <c r="G116" s="18">
         <v>781242</v>
@@ -3627,7 +3627,7 @@
       <c r="I116" s="19"/>
       <c r="J116" s="20"/>
     </row>
-    <row r="117" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="117" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B117" s="15" t="s">
         <v>8</v>
       </c>
@@ -3638,10 +3638,10 @@
         <v>10</v>
       </c>
       <c r="E117" s="16" t="s">
-        <v>64</v>
+        <v>112</v>
       </c>
       <c r="F117" s="18">
-        <v>31249</v>
+        <v>27578</v>
       </c>
       <c r="G117" s="18">
         <v>781242</v>
@@ -3650,21 +3650,21 @@
       <c r="I117" s="19"/>
       <c r="J117" s="20"/>
     </row>
-    <row r="118" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="118" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B118" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C118" s="16" t="s">
-        <v>12</v>
+        <v>113</v>
       </c>
       <c r="D118" s="17" t="s">
-        <v>13</v>
+        <v>114</v>
       </c>
       <c r="E118" s="16" t="s">
-        <v>64</v>
+        <v>11</v>
       </c>
       <c r="F118" s="18">
-        <v>31249</v>
+        <v>19791</v>
       </c>
       <c r="G118" s="18">
         <v>781242</v>
@@ -3673,18 +3673,18 @@
       <c r="I118" s="19"/>
       <c r="J118" s="20"/>
     </row>
-    <row r="119" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="119" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B119" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C119" s="16" t="s">
-        <v>9</v>
+        <v>113</v>
       </c>
       <c r="D119" s="17" t="s">
-        <v>10</v>
+        <v>114</v>
       </c>
       <c r="E119" s="16" t="s">
-        <v>65</v>
+        <v>12</v>
       </c>
       <c r="F119" s="18">
         <v>31249</v>
@@ -3696,18 +3696,18 @@
       <c r="I119" s="19"/>
       <c r="J119" s="20"/>
     </row>
-    <row r="120" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="120" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B120" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C120" s="16" t="s">
-        <v>12</v>
+        <v>113</v>
       </c>
       <c r="D120" s="17" t="s">
+        <v>114</v>
+      </c>
+      <c r="E120" s="16" t="s">
         <v>13</v>
-      </c>
-      <c r="E120" s="16" t="s">
-        <v>65</v>
       </c>
       <c r="F120" s="18">
         <v>31249</v>
@@ -3719,18 +3719,18 @@
       <c r="I120" s="19"/>
       <c r="J120" s="20"/>
     </row>
-    <row r="121" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="121" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B121" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C121" s="16" t="s">
-        <v>9</v>
+        <v>113</v>
       </c>
       <c r="D121" s="17" t="s">
-        <v>10</v>
+        <v>114</v>
       </c>
       <c r="E121" s="16" t="s">
-        <v>66</v>
+        <v>14</v>
       </c>
       <c r="F121" s="18">
         <v>31249</v>
@@ -3742,18 +3742,18 @@
       <c r="I121" s="19"/>
       <c r="J121" s="20"/>
     </row>
-    <row r="122" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="122" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B122" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C122" s="16" t="s">
-        <v>12</v>
+        <v>113</v>
       </c>
       <c r="D122" s="17" t="s">
-        <v>13</v>
+        <v>114</v>
       </c>
       <c r="E122" s="16" t="s">
-        <v>66</v>
+        <v>15</v>
       </c>
       <c r="F122" s="18">
         <v>31249</v>
@@ -3765,18 +3765,18 @@
       <c r="I122" s="19"/>
       <c r="J122" s="20"/>
     </row>
-    <row r="123" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="123" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B123" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C123" s="16" t="s">
-        <v>9</v>
+        <v>113</v>
       </c>
       <c r="D123" s="17" t="s">
-        <v>10</v>
+        <v>114</v>
       </c>
       <c r="E123" s="16" t="s">
-        <v>67</v>
+        <v>16</v>
       </c>
       <c r="F123" s="18">
         <v>31249</v>
@@ -3788,18 +3788,18 @@
       <c r="I123" s="19"/>
       <c r="J123" s="20"/>
     </row>
-    <row r="124" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="124" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B124" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C124" s="16" t="s">
-        <v>12</v>
+        <v>113</v>
       </c>
       <c r="D124" s="17" t="s">
-        <v>13</v>
+        <v>114</v>
       </c>
       <c r="E124" s="16" t="s">
-        <v>67</v>
+        <v>17</v>
       </c>
       <c r="F124" s="18">
         <v>31249</v>
@@ -3811,18 +3811,18 @@
       <c r="I124" s="19"/>
       <c r="J124" s="20"/>
     </row>
-    <row r="125" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="125" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B125" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C125" s="16" t="s">
-        <v>9</v>
+        <v>113</v>
       </c>
       <c r="D125" s="17" t="s">
-        <v>10</v>
+        <v>114</v>
       </c>
       <c r="E125" s="16" t="s">
-        <v>68</v>
+        <v>18</v>
       </c>
       <c r="F125" s="18">
         <v>31249</v>
@@ -3834,18 +3834,18 @@
       <c r="I125" s="19"/>
       <c r="J125" s="20"/>
     </row>
-    <row r="126" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="126" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B126" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C126" s="16" t="s">
-        <v>12</v>
+        <v>113</v>
       </c>
       <c r="D126" s="17" t="s">
-        <v>13</v>
+        <v>114</v>
       </c>
       <c r="E126" s="16" t="s">
-        <v>68</v>
+        <v>19</v>
       </c>
       <c r="F126" s="18">
         <v>31249</v>
@@ -3857,18 +3857,18 @@
       <c r="I126" s="19"/>
       <c r="J126" s="20"/>
     </row>
-    <row r="127" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="127" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B127" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C127" s="16" t="s">
-        <v>9</v>
+        <v>113</v>
       </c>
       <c r="D127" s="17" t="s">
-        <v>10</v>
+        <v>114</v>
       </c>
       <c r="E127" s="16" t="s">
-        <v>69</v>
+        <v>20</v>
       </c>
       <c r="F127" s="18">
         <v>31249</v>
@@ -3880,18 +3880,18 @@
       <c r="I127" s="19"/>
       <c r="J127" s="20"/>
     </row>
-    <row r="128" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="128" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B128" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C128" s="16" t="s">
-        <v>12</v>
+        <v>113</v>
       </c>
       <c r="D128" s="17" t="s">
-        <v>13</v>
+        <v>114</v>
       </c>
       <c r="E128" s="16" t="s">
-        <v>69</v>
+        <v>21</v>
       </c>
       <c r="F128" s="18">
         <v>31249</v>
@@ -3903,18 +3903,18 @@
       <c r="I128" s="19"/>
       <c r="J128" s="20"/>
     </row>
-    <row r="129" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="129" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B129" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C129" s="16" t="s">
-        <v>9</v>
+        <v>113</v>
       </c>
       <c r="D129" s="17" t="s">
-        <v>10</v>
+        <v>114</v>
       </c>
       <c r="E129" s="16" t="s">
-        <v>70</v>
+        <v>22</v>
       </c>
       <c r="F129" s="18">
         <v>31249</v>
@@ -3926,18 +3926,18 @@
       <c r="I129" s="19"/>
       <c r="J129" s="20"/>
     </row>
-    <row r="130" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="130" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B130" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C130" s="16" t="s">
-        <v>12</v>
+        <v>113</v>
       </c>
       <c r="D130" s="17" t="s">
-        <v>13</v>
+        <v>114</v>
       </c>
       <c r="E130" s="16" t="s">
-        <v>70</v>
+        <v>23</v>
       </c>
       <c r="F130" s="18">
         <v>31249</v>
@@ -3949,18 +3949,18 @@
       <c r="I130" s="19"/>
       <c r="J130" s="20"/>
     </row>
-    <row r="131" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="131" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B131" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C131" s="16" t="s">
-        <v>9</v>
+        <v>113</v>
       </c>
       <c r="D131" s="17" t="s">
-        <v>10</v>
+        <v>114</v>
       </c>
       <c r="E131" s="16" t="s">
-        <v>71</v>
+        <v>24</v>
       </c>
       <c r="F131" s="18">
         <v>31249</v>
@@ -3972,18 +3972,18 @@
       <c r="I131" s="19"/>
       <c r="J131" s="20"/>
     </row>
-    <row r="132" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="132" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B132" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C132" s="16" t="s">
-        <v>12</v>
+        <v>113</v>
       </c>
       <c r="D132" s="17" t="s">
-        <v>13</v>
+        <v>114</v>
       </c>
       <c r="E132" s="16" t="s">
-        <v>71</v>
+        <v>25</v>
       </c>
       <c r="F132" s="18">
         <v>31249</v>
@@ -3995,18 +3995,18 @@
       <c r="I132" s="19"/>
       <c r="J132" s="20"/>
     </row>
-    <row r="133" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="133" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B133" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C133" s="16" t="s">
-        <v>9</v>
+        <v>113</v>
       </c>
       <c r="D133" s="17" t="s">
-        <v>10</v>
+        <v>114</v>
       </c>
       <c r="E133" s="16" t="s">
-        <v>72</v>
+        <v>26</v>
       </c>
       <c r="F133" s="18">
         <v>31249</v>
@@ -4018,18 +4018,18 @@
       <c r="I133" s="19"/>
       <c r="J133" s="20"/>
     </row>
-    <row r="134" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="134" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B134" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C134" s="16" t="s">
-        <v>12</v>
+        <v>113</v>
       </c>
       <c r="D134" s="17" t="s">
-        <v>13</v>
+        <v>114</v>
       </c>
       <c r="E134" s="16" t="s">
-        <v>72</v>
+        <v>27</v>
       </c>
       <c r="F134" s="18">
         <v>31249</v>
@@ -4041,18 +4041,18 @@
       <c r="I134" s="19"/>
       <c r="J134" s="20"/>
     </row>
-    <row r="135" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="135" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B135" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C135" s="16" t="s">
-        <v>9</v>
+        <v>113</v>
       </c>
       <c r="D135" s="17" t="s">
-        <v>10</v>
+        <v>114</v>
       </c>
       <c r="E135" s="16" t="s">
-        <v>73</v>
+        <v>28</v>
       </c>
       <c r="F135" s="18">
         <v>31249</v>
@@ -4064,18 +4064,18 @@
       <c r="I135" s="19"/>
       <c r="J135" s="20"/>
     </row>
-    <row r="136" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="136" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B136" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C136" s="16" t="s">
-        <v>12</v>
+        <v>113</v>
       </c>
       <c r="D136" s="17" t="s">
-        <v>13</v>
+        <v>114</v>
       </c>
       <c r="E136" s="16" t="s">
-        <v>73</v>
+        <v>29</v>
       </c>
       <c r="F136" s="18">
         <v>31249</v>
@@ -4087,18 +4087,18 @@
       <c r="I136" s="19"/>
       <c r="J136" s="20"/>
     </row>
-    <row r="137" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="137" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B137" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C137" s="16" t="s">
-        <v>9</v>
+        <v>113</v>
       </c>
       <c r="D137" s="17" t="s">
-        <v>10</v>
+        <v>114</v>
       </c>
       <c r="E137" s="16" t="s">
-        <v>74</v>
+        <v>30</v>
       </c>
       <c r="F137" s="18">
         <v>31249</v>
@@ -4110,18 +4110,18 @@
       <c r="I137" s="19"/>
       <c r="J137" s="20"/>
     </row>
-    <row r="138" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="138" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B138" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C138" s="16" t="s">
-        <v>12</v>
+        <v>113</v>
       </c>
       <c r="D138" s="17" t="s">
-        <v>13</v>
+        <v>114</v>
       </c>
       <c r="E138" s="16" t="s">
-        <v>74</v>
+        <v>31</v>
       </c>
       <c r="F138" s="18">
         <v>31249</v>
@@ -4133,18 +4133,18 @@
       <c r="I138" s="19"/>
       <c r="J138" s="20"/>
     </row>
-    <row r="139" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="139" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B139" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C139" s="16" t="s">
-        <v>9</v>
+        <v>113</v>
       </c>
       <c r="D139" s="17" t="s">
-        <v>10</v>
+        <v>114</v>
       </c>
       <c r="E139" s="16" t="s">
-        <v>75</v>
+        <v>32</v>
       </c>
       <c r="F139" s="18">
         <v>31249</v>
@@ -4156,18 +4156,18 @@
       <c r="I139" s="19"/>
       <c r="J139" s="20"/>
     </row>
-    <row r="140" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="140" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B140" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C140" s="16" t="s">
-        <v>12</v>
+        <v>113</v>
       </c>
       <c r="D140" s="17" t="s">
-        <v>13</v>
+        <v>114</v>
       </c>
       <c r="E140" s="16" t="s">
-        <v>75</v>
+        <v>33</v>
       </c>
       <c r="F140" s="18">
         <v>31249</v>
@@ -4179,18 +4179,18 @@
       <c r="I140" s="19"/>
       <c r="J140" s="20"/>
     </row>
-    <row r="141" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="141" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B141" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C141" s="16" t="s">
-        <v>9</v>
+        <v>113</v>
       </c>
       <c r="D141" s="17" t="s">
-        <v>10</v>
+        <v>114</v>
       </c>
       <c r="E141" s="16" t="s">
-        <v>76</v>
+        <v>34</v>
       </c>
       <c r="F141" s="18">
         <v>31249</v>
@@ -4202,18 +4202,18 @@
       <c r="I141" s="19"/>
       <c r="J141" s="20"/>
     </row>
-    <row r="142" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="142" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B142" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C142" s="16" t="s">
-        <v>12</v>
+        <v>113</v>
       </c>
       <c r="D142" s="17" t="s">
-        <v>13</v>
+        <v>114</v>
       </c>
       <c r="E142" s="16" t="s">
-        <v>76</v>
+        <v>35</v>
       </c>
       <c r="F142" s="18">
         <v>31249</v>
@@ -4225,18 +4225,18 @@
       <c r="I142" s="19"/>
       <c r="J142" s="20"/>
     </row>
-    <row r="143" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="143" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B143" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C143" s="16" t="s">
-        <v>9</v>
+        <v>113</v>
       </c>
       <c r="D143" s="17" t="s">
-        <v>10</v>
+        <v>114</v>
       </c>
       <c r="E143" s="16" t="s">
-        <v>77</v>
+        <v>36</v>
       </c>
       <c r="F143" s="18">
         <v>31249</v>
@@ -4248,18 +4248,18 @@
       <c r="I143" s="19"/>
       <c r="J143" s="20"/>
     </row>
-    <row r="144" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="144" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B144" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C144" s="16" t="s">
-        <v>12</v>
+        <v>113</v>
       </c>
       <c r="D144" s="17" t="s">
-        <v>13</v>
+        <v>114</v>
       </c>
       <c r="E144" s="16" t="s">
-        <v>77</v>
+        <v>37</v>
       </c>
       <c r="F144" s="18">
         <v>31249</v>
@@ -4271,18 +4271,18 @@
       <c r="I144" s="19"/>
       <c r="J144" s="20"/>
     </row>
-    <row r="145" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="145" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B145" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C145" s="16" t="s">
-        <v>9</v>
+        <v>113</v>
       </c>
       <c r="D145" s="17" t="s">
-        <v>10</v>
+        <v>114</v>
       </c>
       <c r="E145" s="16" t="s">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="F145" s="18">
         <v>31249</v>
@@ -4294,18 +4294,18 @@
       <c r="I145" s="19"/>
       <c r="J145" s="20"/>
     </row>
-    <row r="146" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="146" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B146" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C146" s="16" t="s">
-        <v>12</v>
+        <v>113</v>
       </c>
       <c r="D146" s="17" t="s">
-        <v>13</v>
+        <v>114</v>
       </c>
       <c r="E146" s="16" t="s">
-        <v>78</v>
+        <v>39</v>
       </c>
       <c r="F146" s="18">
         <v>31249</v>
@@ -4317,18 +4317,18 @@
       <c r="I146" s="19"/>
       <c r="J146" s="20"/>
     </row>
-    <row r="147" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="147" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B147" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C147" s="16" t="s">
-        <v>9</v>
+        <v>113</v>
       </c>
       <c r="D147" s="17" t="s">
-        <v>10</v>
+        <v>114</v>
       </c>
       <c r="E147" s="16" t="s">
-        <v>79</v>
+        <v>40</v>
       </c>
       <c r="F147" s="18">
         <v>31249</v>
@@ -4340,18 +4340,18 @@
       <c r="I147" s="19"/>
       <c r="J147" s="20"/>
     </row>
-    <row r="148" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="148" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B148" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C148" s="16" t="s">
-        <v>12</v>
+        <v>113</v>
       </c>
       <c r="D148" s="17" t="s">
-        <v>13</v>
+        <v>114</v>
       </c>
       <c r="E148" s="16" t="s">
-        <v>79</v>
+        <v>41</v>
       </c>
       <c r="F148" s="18">
         <v>31249</v>
@@ -4363,18 +4363,18 @@
       <c r="I148" s="19"/>
       <c r="J148" s="20"/>
     </row>
-    <row r="149" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="149" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B149" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C149" s="16" t="s">
-        <v>9</v>
+        <v>113</v>
       </c>
       <c r="D149" s="17" t="s">
-        <v>10</v>
+        <v>114</v>
       </c>
       <c r="E149" s="16" t="s">
-        <v>80</v>
+        <v>42</v>
       </c>
       <c r="F149" s="18">
         <v>31249</v>
@@ -4386,18 +4386,18 @@
       <c r="I149" s="19"/>
       <c r="J149" s="20"/>
     </row>
-    <row r="150" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="150" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B150" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C150" s="16" t="s">
-        <v>12</v>
+        <v>113</v>
       </c>
       <c r="D150" s="17" t="s">
-        <v>13</v>
+        <v>114</v>
       </c>
       <c r="E150" s="16" t="s">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="F150" s="18">
         <v>31249</v>
@@ -4409,18 +4409,18 @@
       <c r="I150" s="19"/>
       <c r="J150" s="20"/>
     </row>
-    <row r="151" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="151" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B151" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C151" s="16" t="s">
-        <v>9</v>
+        <v>113</v>
       </c>
       <c r="D151" s="17" t="s">
-        <v>10</v>
+        <v>114</v>
       </c>
       <c r="E151" s="16" t="s">
-        <v>81</v>
+        <v>44</v>
       </c>
       <c r="F151" s="18">
         <v>31249</v>
@@ -4432,18 +4432,18 @@
       <c r="I151" s="19"/>
       <c r="J151" s="20"/>
     </row>
-    <row r="152" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="152" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B152" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C152" s="16" t="s">
-        <v>12</v>
+        <v>113</v>
       </c>
       <c r="D152" s="17" t="s">
-        <v>13</v>
+        <v>114</v>
       </c>
       <c r="E152" s="16" t="s">
-        <v>81</v>
+        <v>45</v>
       </c>
       <c r="F152" s="18">
         <v>31249</v>
@@ -4455,18 +4455,18 @@
       <c r="I152" s="19"/>
       <c r="J152" s="20"/>
     </row>
-    <row r="153" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="153" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B153" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C153" s="16" t="s">
-        <v>9</v>
+        <v>113</v>
       </c>
       <c r="D153" s="17" t="s">
-        <v>10</v>
+        <v>114</v>
       </c>
       <c r="E153" s="16" t="s">
-        <v>82</v>
+        <v>46</v>
       </c>
       <c r="F153" s="18">
         <v>31249</v>
@@ -4478,18 +4478,18 @@
       <c r="I153" s="19"/>
       <c r="J153" s="20"/>
     </row>
-    <row r="154" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="154" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B154" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C154" s="16" t="s">
-        <v>12</v>
+        <v>113</v>
       </c>
       <c r="D154" s="17" t="s">
-        <v>13</v>
+        <v>114</v>
       </c>
       <c r="E154" s="16" t="s">
-        <v>82</v>
+        <v>47</v>
       </c>
       <c r="F154" s="18">
         <v>31249</v>
@@ -4501,18 +4501,18 @@
       <c r="I154" s="19"/>
       <c r="J154" s="20"/>
     </row>
-    <row r="155" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="155" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B155" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C155" s="16" t="s">
-        <v>9</v>
+        <v>113</v>
       </c>
       <c r="D155" s="17" t="s">
-        <v>10</v>
+        <v>114</v>
       </c>
       <c r="E155" s="16" t="s">
-        <v>83</v>
+        <v>48</v>
       </c>
       <c r="F155" s="18">
         <v>31249</v>
@@ -4524,18 +4524,18 @@
       <c r="I155" s="19"/>
       <c r="J155" s="20"/>
     </row>
-    <row r="156" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="156" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B156" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C156" s="16" t="s">
-        <v>12</v>
+        <v>113</v>
       </c>
       <c r="D156" s="17" t="s">
-        <v>13</v>
+        <v>114</v>
       </c>
       <c r="E156" s="16" t="s">
-        <v>83</v>
+        <v>49</v>
       </c>
       <c r="F156" s="18">
         <v>31249</v>
@@ -4547,18 +4547,18 @@
       <c r="I156" s="19"/>
       <c r="J156" s="20"/>
     </row>
-    <row r="157" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="157" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B157" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C157" s="16" t="s">
-        <v>9</v>
+        <v>113</v>
       </c>
       <c r="D157" s="17" t="s">
-        <v>10</v>
+        <v>114</v>
       </c>
       <c r="E157" s="16" t="s">
-        <v>84</v>
+        <v>50</v>
       </c>
       <c r="F157" s="18">
         <v>31249</v>
@@ -4570,18 +4570,18 @@
       <c r="I157" s="19"/>
       <c r="J157" s="20"/>
     </row>
-    <row r="158" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="158" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B158" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C158" s="16" t="s">
-        <v>12</v>
+        <v>113</v>
       </c>
       <c r="D158" s="17" t="s">
-        <v>13</v>
+        <v>114</v>
       </c>
       <c r="E158" s="16" t="s">
-        <v>84</v>
+        <v>51</v>
       </c>
       <c r="F158" s="18">
         <v>31249</v>
@@ -4593,18 +4593,18 @@
       <c r="I158" s="19"/>
       <c r="J158" s="20"/>
     </row>
-    <row r="159" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="159" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B159" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C159" s="16" t="s">
-        <v>9</v>
+        <v>113</v>
       </c>
       <c r="D159" s="17" t="s">
-        <v>10</v>
+        <v>114</v>
       </c>
       <c r="E159" s="16" t="s">
-        <v>85</v>
+        <v>52</v>
       </c>
       <c r="F159" s="18">
         <v>31249</v>
@@ -4616,18 +4616,18 @@
       <c r="I159" s="19"/>
       <c r="J159" s="20"/>
     </row>
-    <row r="160" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="160" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B160" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C160" s="16" t="s">
-        <v>12</v>
+        <v>113</v>
       </c>
       <c r="D160" s="17" t="s">
-        <v>13</v>
+        <v>114</v>
       </c>
       <c r="E160" s="16" t="s">
-        <v>85</v>
+        <v>53</v>
       </c>
       <c r="F160" s="18">
         <v>31249</v>
@@ -4639,18 +4639,18 @@
       <c r="I160" s="19"/>
       <c r="J160" s="20"/>
     </row>
-    <row r="161" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="161" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B161" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C161" s="16" t="s">
-        <v>9</v>
+        <v>113</v>
       </c>
       <c r="D161" s="17" t="s">
-        <v>10</v>
+        <v>114</v>
       </c>
       <c r="E161" s="16" t="s">
-        <v>86</v>
+        <v>54</v>
       </c>
       <c r="F161" s="18">
         <v>31249</v>
@@ -4662,18 +4662,18 @@
       <c r="I161" s="19"/>
       <c r="J161" s="20"/>
     </row>
-    <row r="162" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="162" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B162" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C162" s="16" t="s">
-        <v>12</v>
+        <v>113</v>
       </c>
       <c r="D162" s="17" t="s">
-        <v>13</v>
+        <v>114</v>
       </c>
       <c r="E162" s="16" t="s">
-        <v>86</v>
+        <v>55</v>
       </c>
       <c r="F162" s="18">
         <v>31249</v>
@@ -4685,18 +4685,18 @@
       <c r="I162" s="19"/>
       <c r="J162" s="20"/>
     </row>
-    <row r="163" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="163" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B163" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C163" s="16" t="s">
-        <v>9</v>
+        <v>113</v>
       </c>
       <c r="D163" s="17" t="s">
-        <v>10</v>
+        <v>114</v>
       </c>
       <c r="E163" s="16" t="s">
-        <v>87</v>
+        <v>56</v>
       </c>
       <c r="F163" s="18">
         <v>31249</v>
@@ -4708,18 +4708,18 @@
       <c r="I163" s="19"/>
       <c r="J163" s="20"/>
     </row>
-    <row r="164" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="164" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B164" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C164" s="16" t="s">
-        <v>12</v>
+        <v>113</v>
       </c>
       <c r="D164" s="17" t="s">
-        <v>13</v>
+        <v>114</v>
       </c>
       <c r="E164" s="16" t="s">
-        <v>87</v>
+        <v>57</v>
       </c>
       <c r="F164" s="18">
         <v>31249</v>
@@ -4731,18 +4731,18 @@
       <c r="I164" s="19"/>
       <c r="J164" s="20"/>
     </row>
-    <row r="165" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="165" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B165" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C165" s="16" t="s">
-        <v>9</v>
+        <v>113</v>
       </c>
       <c r="D165" s="17" t="s">
-        <v>10</v>
+        <v>114</v>
       </c>
       <c r="E165" s="16" t="s">
-        <v>88</v>
+        <v>58</v>
       </c>
       <c r="F165" s="18">
         <v>31249</v>
@@ -4754,18 +4754,18 @@
       <c r="I165" s="19"/>
       <c r="J165" s="20"/>
     </row>
-    <row r="166" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="166" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B166" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C166" s="16" t="s">
-        <v>12</v>
+        <v>113</v>
       </c>
       <c r="D166" s="17" t="s">
-        <v>13</v>
+        <v>114</v>
       </c>
       <c r="E166" s="16" t="s">
-        <v>88</v>
+        <v>59</v>
       </c>
       <c r="F166" s="18">
         <v>31249</v>
@@ -4777,18 +4777,18 @@
       <c r="I166" s="19"/>
       <c r="J166" s="20"/>
     </row>
-    <row r="167" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="167" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B167" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C167" s="16" t="s">
-        <v>9</v>
+        <v>113</v>
       </c>
       <c r="D167" s="17" t="s">
-        <v>10</v>
+        <v>114</v>
       </c>
       <c r="E167" s="16" t="s">
-        <v>89</v>
+        <v>60</v>
       </c>
       <c r="F167" s="18">
         <v>31249</v>
@@ -4800,18 +4800,18 @@
       <c r="I167" s="19"/>
       <c r="J167" s="20"/>
     </row>
-    <row r="168" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="168" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B168" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C168" s="16" t="s">
-        <v>12</v>
+        <v>113</v>
       </c>
       <c r="D168" s="17" t="s">
-        <v>13</v>
+        <v>114</v>
       </c>
       <c r="E168" s="16" t="s">
-        <v>89</v>
+        <v>61</v>
       </c>
       <c r="F168" s="18">
         <v>31249</v>
@@ -4823,18 +4823,18 @@
       <c r="I168" s="19"/>
       <c r="J168" s="20"/>
     </row>
-    <row r="169" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="169" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B169" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C169" s="16" t="s">
-        <v>9</v>
+        <v>113</v>
       </c>
       <c r="D169" s="17" t="s">
-        <v>10</v>
+        <v>114</v>
       </c>
       <c r="E169" s="16" t="s">
-        <v>90</v>
+        <v>62</v>
       </c>
       <c r="F169" s="18">
         <v>31249</v>
@@ -4846,18 +4846,18 @@
       <c r="I169" s="19"/>
       <c r="J169" s="20"/>
     </row>
-    <row r="170" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="170" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B170" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C170" s="16" t="s">
-        <v>12</v>
+        <v>113</v>
       </c>
       <c r="D170" s="17" t="s">
-        <v>13</v>
+        <v>114</v>
       </c>
       <c r="E170" s="16" t="s">
-        <v>90</v>
+        <v>63</v>
       </c>
       <c r="F170" s="18">
         <v>31249</v>
@@ -4869,18 +4869,18 @@
       <c r="I170" s="19"/>
       <c r="J170" s="20"/>
     </row>
-    <row r="171" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="171" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B171" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C171" s="16" t="s">
-        <v>9</v>
+        <v>113</v>
       </c>
       <c r="D171" s="17" t="s">
-        <v>10</v>
+        <v>114</v>
       </c>
       <c r="E171" s="16" t="s">
-        <v>91</v>
+        <v>64</v>
       </c>
       <c r="F171" s="18">
         <v>31249</v>
@@ -4892,18 +4892,18 @@
       <c r="I171" s="19"/>
       <c r="J171" s="20"/>
     </row>
-    <row r="172" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="172" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B172" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C172" s="16" t="s">
-        <v>12</v>
+        <v>113</v>
       </c>
       <c r="D172" s="17" t="s">
-        <v>13</v>
+        <v>114</v>
       </c>
       <c r="E172" s="16" t="s">
-        <v>91</v>
+        <v>65</v>
       </c>
       <c r="F172" s="18">
         <v>31249</v>
@@ -4915,18 +4915,18 @@
       <c r="I172" s="19"/>
       <c r="J172" s="20"/>
     </row>
-    <row r="173" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="173" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B173" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C173" s="16" t="s">
-        <v>9</v>
+        <v>113</v>
       </c>
       <c r="D173" s="17" t="s">
-        <v>10</v>
+        <v>114</v>
       </c>
       <c r="E173" s="16" t="s">
-        <v>92</v>
+        <v>66</v>
       </c>
       <c r="F173" s="18">
         <v>31249</v>
@@ -4938,18 +4938,18 @@
       <c r="I173" s="19"/>
       <c r="J173" s="20"/>
     </row>
-    <row r="174" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="174" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B174" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C174" s="16" t="s">
-        <v>12</v>
+        <v>113</v>
       </c>
       <c r="D174" s="17" t="s">
-        <v>13</v>
+        <v>114</v>
       </c>
       <c r="E174" s="16" t="s">
-        <v>92</v>
+        <v>67</v>
       </c>
       <c r="F174" s="18">
         <v>31249</v>
@@ -4961,18 +4961,18 @@
       <c r="I174" s="19"/>
       <c r="J174" s="20"/>
     </row>
-    <row r="175" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="175" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B175" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C175" s="16" t="s">
-        <v>9</v>
+        <v>113</v>
       </c>
       <c r="D175" s="17" t="s">
-        <v>10</v>
+        <v>114</v>
       </c>
       <c r="E175" s="16" t="s">
-        <v>93</v>
+        <v>68</v>
       </c>
       <c r="F175" s="18">
         <v>31249</v>
@@ -4984,18 +4984,18 @@
       <c r="I175" s="19"/>
       <c r="J175" s="20"/>
     </row>
-    <row r="176" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="176" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B176" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C176" s="16" t="s">
-        <v>12</v>
+        <v>113</v>
       </c>
       <c r="D176" s="17" t="s">
-        <v>13</v>
+        <v>114</v>
       </c>
       <c r="E176" s="16" t="s">
-        <v>93</v>
+        <v>69</v>
       </c>
       <c r="F176" s="18">
         <v>31249</v>
@@ -5007,18 +5007,18 @@
       <c r="I176" s="19"/>
       <c r="J176" s="20"/>
     </row>
-    <row r="177" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="177" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B177" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C177" s="16" t="s">
-        <v>9</v>
+        <v>113</v>
       </c>
       <c r="D177" s="17" t="s">
-        <v>10</v>
+        <v>114</v>
       </c>
       <c r="E177" s="16" t="s">
-        <v>94</v>
+        <v>70</v>
       </c>
       <c r="F177" s="18">
         <v>31249</v>
@@ -5030,18 +5030,18 @@
       <c r="I177" s="19"/>
       <c r="J177" s="20"/>
     </row>
-    <row r="178" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="178" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B178" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C178" s="16" t="s">
-        <v>12</v>
+        <v>113</v>
       </c>
       <c r="D178" s="17" t="s">
-        <v>13</v>
+        <v>114</v>
       </c>
       <c r="E178" s="16" t="s">
-        <v>94</v>
+        <v>71</v>
       </c>
       <c r="F178" s="18">
         <v>31249</v>
@@ -5053,18 +5053,18 @@
       <c r="I178" s="19"/>
       <c r="J178" s="20"/>
     </row>
-    <row r="179" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="179" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B179" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C179" s="16" t="s">
-        <v>9</v>
+        <v>113</v>
       </c>
       <c r="D179" s="17" t="s">
-        <v>10</v>
+        <v>114</v>
       </c>
       <c r="E179" s="16" t="s">
-        <v>95</v>
+        <v>72</v>
       </c>
       <c r="F179" s="18">
         <v>31249</v>
@@ -5076,18 +5076,18 @@
       <c r="I179" s="19"/>
       <c r="J179" s="20"/>
     </row>
-    <row r="180" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="180" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B180" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C180" s="16" t="s">
-        <v>12</v>
+        <v>113</v>
       </c>
       <c r="D180" s="17" t="s">
-        <v>13</v>
+        <v>114</v>
       </c>
       <c r="E180" s="16" t="s">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="F180" s="18">
         <v>31249</v>
@@ -5099,18 +5099,18 @@
       <c r="I180" s="19"/>
       <c r="J180" s="20"/>
     </row>
-    <row r="181" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="181" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B181" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C181" s="16" t="s">
-        <v>9</v>
+        <v>113</v>
       </c>
       <c r="D181" s="17" t="s">
-        <v>10</v>
+        <v>114</v>
       </c>
       <c r="E181" s="16" t="s">
-        <v>96</v>
+        <v>74</v>
       </c>
       <c r="F181" s="18">
         <v>31249</v>
@@ -5122,18 +5122,18 @@
       <c r="I181" s="19"/>
       <c r="J181" s="20"/>
     </row>
-    <row r="182" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="182" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B182" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C182" s="16" t="s">
-        <v>12</v>
+        <v>113</v>
       </c>
       <c r="D182" s="17" t="s">
-        <v>13</v>
+        <v>114</v>
       </c>
       <c r="E182" s="16" t="s">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="F182" s="18">
         <v>31249</v>
@@ -5145,18 +5145,18 @@
       <c r="I182" s="19"/>
       <c r="J182" s="20"/>
     </row>
-    <row r="183" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="183" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B183" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C183" s="16" t="s">
-        <v>9</v>
+        <v>113</v>
       </c>
       <c r="D183" s="17" t="s">
-        <v>10</v>
+        <v>114</v>
       </c>
       <c r="E183" s="16" t="s">
-        <v>97</v>
+        <v>76</v>
       </c>
       <c r="F183" s="18">
         <v>31249</v>
@@ -5168,18 +5168,18 @@
       <c r="I183" s="19"/>
       <c r="J183" s="20"/>
     </row>
-    <row r="184" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="184" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B184" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C184" s="16" t="s">
-        <v>12</v>
+        <v>113</v>
       </c>
       <c r="D184" s="17" t="s">
-        <v>13</v>
+        <v>114</v>
       </c>
       <c r="E184" s="16" t="s">
-        <v>97</v>
+        <v>77</v>
       </c>
       <c r="F184" s="18">
         <v>31249</v>
@@ -5191,18 +5191,18 @@
       <c r="I184" s="19"/>
       <c r="J184" s="20"/>
     </row>
-    <row r="185" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="185" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B185" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C185" s="16" t="s">
-        <v>9</v>
+        <v>113</v>
       </c>
       <c r="D185" s="17" t="s">
-        <v>10</v>
+        <v>114</v>
       </c>
       <c r="E185" s="16" t="s">
-        <v>98</v>
+        <v>78</v>
       </c>
       <c r="F185" s="18">
         <v>31249</v>
@@ -5214,18 +5214,18 @@
       <c r="I185" s="19"/>
       <c r="J185" s="20"/>
     </row>
-    <row r="186" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="186" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B186" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C186" s="16" t="s">
-        <v>12</v>
+        <v>113</v>
       </c>
       <c r="D186" s="17" t="s">
-        <v>13</v>
+        <v>114</v>
       </c>
       <c r="E186" s="16" t="s">
-        <v>98</v>
+        <v>79</v>
       </c>
       <c r="F186" s="18">
         <v>31249</v>
@@ -5237,18 +5237,18 @@
       <c r="I186" s="19"/>
       <c r="J186" s="20"/>
     </row>
-    <row r="187" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="187" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B187" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C187" s="16" t="s">
-        <v>9</v>
+        <v>113</v>
       </c>
       <c r="D187" s="17" t="s">
-        <v>10</v>
+        <v>114</v>
       </c>
       <c r="E187" s="16" t="s">
-        <v>99</v>
+        <v>80</v>
       </c>
       <c r="F187" s="18">
         <v>31249</v>
@@ -5260,18 +5260,18 @@
       <c r="I187" s="19"/>
       <c r="J187" s="20"/>
     </row>
-    <row r="188" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="188" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B188" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C188" s="16" t="s">
-        <v>12</v>
+        <v>113</v>
       </c>
       <c r="D188" s="17" t="s">
-        <v>13</v>
+        <v>114</v>
       </c>
       <c r="E188" s="16" t="s">
-        <v>99</v>
+        <v>81</v>
       </c>
       <c r="F188" s="18">
         <v>31249</v>
@@ -5283,18 +5283,18 @@
       <c r="I188" s="19"/>
       <c r="J188" s="20"/>
     </row>
-    <row r="189" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="189" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B189" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C189" s="16" t="s">
-        <v>9</v>
+        <v>113</v>
       </c>
       <c r="D189" s="17" t="s">
-        <v>10</v>
+        <v>114</v>
       </c>
       <c r="E189" s="16" t="s">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="F189" s="18">
         <v>31249</v>
@@ -5306,18 +5306,18 @@
       <c r="I189" s="19"/>
       <c r="J189" s="20"/>
     </row>
-    <row r="190" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="190" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B190" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C190" s="16" t="s">
-        <v>12</v>
+        <v>113</v>
       </c>
       <c r="D190" s="17" t="s">
-        <v>13</v>
+        <v>114</v>
       </c>
       <c r="E190" s="16" t="s">
-        <v>100</v>
+        <v>83</v>
       </c>
       <c r="F190" s="18">
         <v>31249</v>
@@ -5329,18 +5329,18 @@
       <c r="I190" s="19"/>
       <c r="J190" s="20"/>
     </row>
-    <row r="191" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="191" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B191" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C191" s="16" t="s">
-        <v>9</v>
+        <v>113</v>
       </c>
       <c r="D191" s="17" t="s">
-        <v>10</v>
+        <v>114</v>
       </c>
       <c r="E191" s="16" t="s">
-        <v>101</v>
+        <v>84</v>
       </c>
       <c r="F191" s="18">
         <v>31249</v>
@@ -5352,18 +5352,18 @@
       <c r="I191" s="19"/>
       <c r="J191" s="20"/>
     </row>
-    <row r="192" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="192" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B192" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C192" s="16" t="s">
-        <v>12</v>
+        <v>113</v>
       </c>
       <c r="D192" s="17" t="s">
-        <v>13</v>
+        <v>114</v>
       </c>
       <c r="E192" s="16" t="s">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="F192" s="18">
         <v>31249</v>
@@ -5375,18 +5375,18 @@
       <c r="I192" s="19"/>
       <c r="J192" s="20"/>
     </row>
-    <row r="193" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="193" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B193" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C193" s="16" t="s">
-        <v>9</v>
+        <v>113</v>
       </c>
       <c r="D193" s="17" t="s">
-        <v>10</v>
+        <v>114</v>
       </c>
       <c r="E193" s="16" t="s">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="F193" s="18">
         <v>31249</v>
@@ -5398,18 +5398,18 @@
       <c r="I193" s="19"/>
       <c r="J193" s="20"/>
     </row>
-    <row r="194" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="194" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B194" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C194" s="16" t="s">
-        <v>12</v>
+        <v>113</v>
       </c>
       <c r="D194" s="17" t="s">
-        <v>13</v>
+        <v>114</v>
       </c>
       <c r="E194" s="16" t="s">
-        <v>102</v>
+        <v>87</v>
       </c>
       <c r="F194" s="18">
         <v>31249</v>
@@ -5421,18 +5421,18 @@
       <c r="I194" s="19"/>
       <c r="J194" s="20"/>
     </row>
-    <row r="195" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="195" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B195" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C195" s="16" t="s">
-        <v>9</v>
+        <v>113</v>
       </c>
       <c r="D195" s="17" t="s">
-        <v>10</v>
+        <v>114</v>
       </c>
       <c r="E195" s="16" t="s">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="F195" s="18">
         <v>31249</v>
@@ -5444,21 +5444,21 @@
       <c r="I195" s="19"/>
       <c r="J195" s="20"/>
     </row>
-    <row r="196" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="196" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B196" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C196" s="16" t="s">
-        <v>12</v>
+        <v>113</v>
       </c>
       <c r="D196" s="17" t="s">
-        <v>13</v>
+        <v>114</v>
       </c>
       <c r="E196" s="16" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="F196" s="18">
-        <v>31249</v>
+        <v>27578</v>
       </c>
       <c r="G196" s="18">
         <v>781242</v>
@@ -5467,21 +5467,21 @@
       <c r="I196" s="19"/>
       <c r="J196" s="20"/>
     </row>
-    <row r="197" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="197" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B197" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C197" s="16" t="s">
-        <v>9</v>
+        <v>113</v>
       </c>
       <c r="D197" s="17" t="s">
-        <v>10</v>
+        <v>114</v>
       </c>
       <c r="E197" s="16" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="F197" s="18">
-        <v>31249</v>
+        <v>27578</v>
       </c>
       <c r="G197" s="18">
         <v>781242</v>
@@ -5490,21 +5490,21 @@
       <c r="I197" s="19"/>
       <c r="J197" s="20"/>
     </row>
-    <row r="198" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="198" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B198" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C198" s="16" t="s">
-        <v>12</v>
+        <v>113</v>
       </c>
       <c r="D198" s="17" t="s">
-        <v>13</v>
+        <v>114</v>
       </c>
       <c r="E198" s="16" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="F198" s="18">
-        <v>31249</v>
+        <v>27578</v>
       </c>
       <c r="G198" s="18">
         <v>781242</v>
@@ -5513,21 +5513,21 @@
       <c r="I198" s="19"/>
       <c r="J198" s="20"/>
     </row>
-    <row r="199" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="199" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B199" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C199" s="16" t="s">
-        <v>9</v>
+        <v>113</v>
       </c>
       <c r="D199" s="17" t="s">
-        <v>10</v>
+        <v>114</v>
       </c>
       <c r="E199" s="16" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
       <c r="F199" s="18">
-        <v>31249</v>
+        <v>27578</v>
       </c>
       <c r="G199" s="18">
         <v>781242</v>
@@ -5536,21 +5536,21 @@
       <c r="I199" s="19"/>
       <c r="J199" s="20"/>
     </row>
-    <row r="200" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="200" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B200" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C200" s="16" t="s">
-        <v>12</v>
+        <v>113</v>
       </c>
       <c r="D200" s="17" t="s">
-        <v>13</v>
+        <v>114</v>
       </c>
       <c r="E200" s="16" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="F200" s="18">
-        <v>31249</v>
+        <v>27578</v>
       </c>
       <c r="G200" s="18">
         <v>781242</v>
@@ -5559,21 +5559,21 @@
       <c r="I200" s="19"/>
       <c r="J200" s="20"/>
     </row>
-    <row r="201" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="201" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B201" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C201" s="16" t="s">
-        <v>9</v>
+        <v>113</v>
       </c>
       <c r="D201" s="17" t="s">
-        <v>10</v>
+        <v>114</v>
       </c>
       <c r="E201" s="16" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="F201" s="18">
-        <v>31249</v>
+        <v>27578</v>
       </c>
       <c r="G201" s="18">
         <v>781242</v>
@@ -5582,21 +5582,21 @@
       <c r="I201" s="19"/>
       <c r="J201" s="20"/>
     </row>
-    <row r="202" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="202" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B202" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C202" s="16" t="s">
-        <v>12</v>
+        <v>113</v>
       </c>
       <c r="D202" s="17" t="s">
-        <v>13</v>
+        <v>114</v>
       </c>
       <c r="E202" s="16" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="F202" s="18">
-        <v>31249</v>
+        <v>27578</v>
       </c>
       <c r="G202" s="18">
         <v>781242</v>
@@ -5605,21 +5605,21 @@
       <c r="I202" s="19"/>
       <c r="J202" s="20"/>
     </row>
-    <row r="203" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="203" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B203" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C203" s="16" t="s">
-        <v>9</v>
+        <v>113</v>
       </c>
       <c r="D203" s="17" t="s">
-        <v>10</v>
+        <v>114</v>
       </c>
       <c r="E203" s="16" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="F203" s="18">
-        <v>31249</v>
+        <v>27578</v>
       </c>
       <c r="G203" s="18">
         <v>781242</v>
@@ -5628,21 +5628,21 @@
       <c r="I203" s="19"/>
       <c r="J203" s="20"/>
     </row>
-    <row r="204" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="204" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B204" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C204" s="16" t="s">
-        <v>12</v>
+        <v>113</v>
       </c>
       <c r="D204" s="17" t="s">
-        <v>13</v>
+        <v>114</v>
       </c>
       <c r="E204" s="16" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="F204" s="18">
-        <v>31249</v>
+        <v>27578</v>
       </c>
       <c r="G204" s="18">
         <v>781242</v>
@@ -5651,21 +5651,21 @@
       <c r="I204" s="19"/>
       <c r="J204" s="20"/>
     </row>
-    <row r="205" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="205" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B205" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C205" s="16" t="s">
-        <v>9</v>
+        <v>113</v>
       </c>
       <c r="D205" s="17" t="s">
-        <v>10</v>
+        <v>114</v>
       </c>
       <c r="E205" s="16" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="F205" s="18">
-        <v>31249</v>
+        <v>27578</v>
       </c>
       <c r="G205" s="18">
         <v>781242</v>
@@ -5674,21 +5674,21 @@
       <c r="I205" s="19"/>
       <c r="J205" s="20"/>
     </row>
-    <row r="206" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="206" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B206" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C206" s="16" t="s">
-        <v>12</v>
+        <v>113</v>
       </c>
       <c r="D206" s="17" t="s">
-        <v>13</v>
+        <v>114</v>
       </c>
       <c r="E206" s="16" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="F206" s="18">
-        <v>31249</v>
+        <v>27578</v>
       </c>
       <c r="G206" s="18">
         <v>781242</v>
@@ -5697,21 +5697,21 @@
       <c r="I206" s="19"/>
       <c r="J206" s="20"/>
     </row>
-    <row r="207" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="207" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B207" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C207" s="16" t="s">
-        <v>9</v>
+        <v>113</v>
       </c>
       <c r="D207" s="17" t="s">
-        <v>10</v>
+        <v>114</v>
       </c>
       <c r="E207" s="16" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="F207" s="18">
-        <v>31249</v>
+        <v>27578</v>
       </c>
       <c r="G207" s="18">
         <v>781242</v>
@@ -5720,21 +5720,21 @@
       <c r="I207" s="19"/>
       <c r="J207" s="20"/>
     </row>
-    <row r="208" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="208" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B208" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C208" s="16" t="s">
-        <v>12</v>
+        <v>113</v>
       </c>
       <c r="D208" s="17" t="s">
-        <v>13</v>
+        <v>114</v>
       </c>
       <c r="E208" s="16" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="F208" s="18">
-        <v>31249</v>
+        <v>27578</v>
       </c>
       <c r="G208" s="18">
         <v>781242</v>
@@ -5743,21 +5743,21 @@
       <c r="I208" s="19"/>
       <c r="J208" s="20"/>
     </row>
-    <row r="209" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="209" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B209" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C209" s="16" t="s">
-        <v>9</v>
+        <v>113</v>
       </c>
       <c r="D209" s="17" t="s">
-        <v>10</v>
+        <v>114</v>
       </c>
       <c r="E209" s="16" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="F209" s="18">
-        <v>31249</v>
+        <v>27578</v>
       </c>
       <c r="G209" s="18">
         <v>781242</v>
@@ -5766,21 +5766,21 @@
       <c r="I209" s="19"/>
       <c r="J209" s="20"/>
     </row>
-    <row r="210" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="210" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B210" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C210" s="16" t="s">
-        <v>12</v>
+        <v>113</v>
       </c>
       <c r="D210" s="17" t="s">
-        <v>13</v>
+        <v>114</v>
       </c>
       <c r="E210" s="16" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="F210" s="18">
-        <v>31249</v>
+        <v>27578</v>
       </c>
       <c r="G210" s="18">
         <v>781242</v>
@@ -5789,21 +5789,21 @@
       <c r="I210" s="19"/>
       <c r="J210" s="20"/>
     </row>
-    <row r="211" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="211" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B211" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C211" s="16" t="s">
-        <v>9</v>
+        <v>113</v>
       </c>
       <c r="D211" s="17" t="s">
-        <v>10</v>
+        <v>114</v>
       </c>
       <c r="E211" s="16" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="F211" s="18">
-        <v>31249</v>
+        <v>27578</v>
       </c>
       <c r="G211" s="18">
         <v>781242</v>
@@ -5812,21 +5812,21 @@
       <c r="I211" s="19"/>
       <c r="J211" s="20"/>
     </row>
-    <row r="212" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="212" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B212" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C212" s="16" t="s">
-        <v>12</v>
+        <v>113</v>
       </c>
       <c r="D212" s="17" t="s">
-        <v>13</v>
+        <v>114</v>
       </c>
       <c r="E212" s="16" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="F212" s="18">
-        <v>31249</v>
+        <v>27578</v>
       </c>
       <c r="G212" s="18">
         <v>781242</v>
@@ -5835,21 +5835,21 @@
       <c r="I212" s="19"/>
       <c r="J212" s="20"/>
     </row>
-    <row r="213" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="213" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B213" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C213" s="16" t="s">
-        <v>9</v>
+        <v>113</v>
       </c>
       <c r="D213" s="17" t="s">
-        <v>10</v>
+        <v>114</v>
       </c>
       <c r="E213" s="16" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="F213" s="18">
-        <v>31249</v>
+        <v>27578</v>
       </c>
       <c r="G213" s="18">
         <v>781242</v>
@@ -5858,21 +5858,21 @@
       <c r="I213" s="19"/>
       <c r="J213" s="20"/>
     </row>
-    <row r="214" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="214" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B214" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C214" s="16" t="s">
-        <v>12</v>
+        <v>113</v>
       </c>
       <c r="D214" s="17" t="s">
-        <v>13</v>
+        <v>114</v>
       </c>
       <c r="E214" s="16" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="F214" s="18">
-        <v>31249</v>
+        <v>27578</v>
       </c>
       <c r="G214" s="18">
         <v>781242</v>
@@ -5881,21 +5881,21 @@
       <c r="I214" s="19"/>
       <c r="J214" s="20"/>
     </row>
-    <row r="215" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="215" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B215" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C215" s="16" t="s">
-        <v>9</v>
+        <v>113</v>
       </c>
       <c r="D215" s="17" t="s">
-        <v>10</v>
+        <v>114</v>
       </c>
       <c r="E215" s="16" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="F215" s="18">
-        <v>31249</v>
+        <v>27578</v>
       </c>
       <c r="G215" s="18">
         <v>781242</v>
@@ -5904,21 +5904,21 @@
       <c r="I215" s="19"/>
       <c r="J215" s="20"/>
     </row>
-    <row r="216" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="216" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B216" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C216" s="16" t="s">
-        <v>12</v>
+        <v>113</v>
       </c>
       <c r="D216" s="17" t="s">
-        <v>13</v>
+        <v>114</v>
       </c>
       <c r="E216" s="16" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="F216" s="18">
-        <v>31249</v>
+        <v>27578</v>
       </c>
       <c r="G216" s="18">
         <v>781242</v>
@@ -5927,21 +5927,21 @@
       <c r="I216" s="19"/>
       <c r="J216" s="20"/>
     </row>
-    <row r="217" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="217" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B217" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C217" s="16" t="s">
-        <v>9</v>
+        <v>113</v>
       </c>
       <c r="D217" s="17" t="s">
-        <v>10</v>
+        <v>114</v>
       </c>
       <c r="E217" s="16" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="F217" s="18">
-        <v>19791</v>
+        <v>27578</v>
       </c>
       <c r="G217" s="18">
         <v>781242</v>
@@ -5950,21 +5950,21 @@
       <c r="I217" s="19"/>
       <c r="J217" s="20"/>
     </row>
-    <row r="218" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="218" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B218" s="21" t="s">
         <v>8</v>
       </c>
       <c r="C218" s="22" t="s">
-        <v>12</v>
+        <v>113</v>
       </c>
       <c r="D218" s="23" t="s">
-        <v>13</v>
+        <v>114</v>
       </c>
       <c r="E218" s="22" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="F218" s="24">
-        <v>19791</v>
+        <v>27578</v>
       </c>
       <c r="G218" s="24">
         <v>781242</v>
@@ -5973,7 +5973,7 @@
       <c r="I218" s="25"/>
       <c r="J218" s="26"/>
     </row>
-    <row r="223" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="223" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B223" s="32" t="s">
         <v>124</v>
       </c>
@@ -5984,7 +5984,7 @@
       <c r="I223" s="1"/>
       <c r="J223" s="1"/>
     </row>
-    <row r="224" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="224" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B224" s="32" t="s">
         <v>123</v>
       </c>
